--- a/summary/yes/exposures_meta_analysis_prostate_cancer_excluding_aggressive_combined.xlsx
+++ b/summary/yes/exposures_meta_analysis_prostate_cancer_excluding_aggressive_combined.xlsx
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,13 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -452,57 +464,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -514,28 +526,28 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="2" t="n">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>102</v>
       </c>
     </row>
@@ -545,28 +557,28 @@
           <t>natto</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>0.28</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.06</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="2" t="n">
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>140</v>
       </c>
     </row>
@@ -576,28 +588,28 @@
           <t>papaya</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>35</v>
       </c>
     </row>
@@ -607,28 +619,28 @@
           <t>early_time_restricted_eating</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="3" t="n">
         <v>1455</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>607</v>
       </c>
     </row>
@@ -638,34 +650,34 @@
           <t>soy</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>0.17</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="4" t="n">
         <v>2.09</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="I6" s="5" t="n">
-        <v>0.1010785350953814</v>
-      </c>
-      <c r="J6" s="2" t="n">
+      <c r="I6" s="6" t="n">
+        <v>0.1010785350953813</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>85059</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>5399</v>
       </c>
     </row>
@@ -675,28 +687,28 @@
           <t>low_fat_diet</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="n">
+      <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="2" t="n">
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
         <v>1170</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>390</v>
       </c>
     </row>
@@ -706,34 +718,34 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="4" t="n">
         <v>0.17</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="4" t="n">
         <v>2.35</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="5" t="n">
         <v>76.2</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I8" s="6" t="n">
         <v>0.2620449311218541</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="3" t="n">
         <v>49170</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>1463</v>
       </c>
     </row>
@@ -743,28 +755,28 @@
           <t>vitamin_k2</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="B9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.39</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="2" t="n">
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="3" t="n">
         <v>11319</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="3" t="n">
         <v>268</v>
       </c>
     </row>
@@ -774,34 +786,34 @@
           <t>genistein</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>0.52</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="5" t="n">
         <v>50.6</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I10" s="6" t="n">
         <v>0.001566293494770549</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="3" t="n">
         <v>64298</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>3531</v>
       </c>
     </row>
@@ -811,34 +823,34 @@
           <t>zeaxanthin</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="4" t="n">
         <v>0.09</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="4" t="n">
         <v>4.89</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="5" t="n">
         <v>62.9</v>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I11" s="6" t="n">
         <v>0.8236639670954942</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" s="3" t="n">
         <v>2106</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="3" t="n">
         <v>808</v>
       </c>
     </row>
@@ -848,28 +860,28 @@
           <t>quercetin</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3" t="n">
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="2" t="n">
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="3" t="n">
         <v>971</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>433</v>
       </c>
     </row>
@@ -879,28 +891,28 @@
           <t>vegan_diet</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3" t="n">
+      <c r="B13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>0.51</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="2" t="n">
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="3" t="n">
         <v>26346</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>1079</v>
       </c>
     </row>
@@ -910,28 +922,28 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="4" t="n">
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="5" t="n">
         <v>80.7</v>
       </c>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="2" t="n">
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="3" t="n">
         <v>57649</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>6553</v>
       </c>
     </row>
@@ -941,28 +953,28 @@
           <t>pyruvate</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="n">
+      <c r="B15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>0.52</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="2" t="n">
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="3" t="n">
         <v>666</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="3" t="n">
         <v>333</v>
       </c>
     </row>
@@ -972,34 +984,34 @@
           <t>garlic</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>265.07</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I16" s="6" t="n">
         <v>0.2044018200861738</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" s="3" t="n">
         <v>36604</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>2168</v>
       </c>
     </row>
@@ -1009,28 +1021,28 @@
           <t>vegetarian_diet</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3" t="n">
+      <c r="B17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="2" t="n">
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="3" t="n">
         <v>217937</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="3" t="n">
         <v>9501</v>
       </c>
     </row>
@@ -1040,34 +1052,34 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="4" t="n">
         <v>0.26</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="5" t="n">
         <v>70.5</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="I18" s="6" t="n">
         <v>0.4789848163683069</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J18" s="3" t="n">
         <v>8735</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>3057</v>
       </c>
     </row>
@@ -1077,28 +1089,28 @@
           <t>vitamin_k</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <v>0.58</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="2" t="n">
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="3" t="n">
         <v>12063</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="3" t="n">
         <v>518</v>
       </c>
     </row>
@@ -1108,34 +1120,34 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="4" t="n">
         <v>0.47</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="5" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="I20" s="5" t="n">
-        <v>2.045420729252858e-05</v>
-      </c>
-      <c r="J20" s="2" t="n">
+      <c r="I20" s="6" t="n">
+        <v>2.045420729252859e-05</v>
+      </c>
+      <c r="J20" s="3" t="n">
         <v>1057923</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="3" t="n">
         <v>67108</v>
       </c>
     </row>
@@ -1145,34 +1157,34 @@
           <t>melatonin</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>196.29</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="I21" s="6" t="n">
         <v>0.0645864721910966</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J21" s="3" t="n">
         <v>4618</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="3" t="n">
         <v>1414</v>
       </c>
     </row>
@@ -1182,28 +1194,28 @@
           <t>citrulline</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="3" t="n">
+      <c r="B22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="2" t="n">
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
         <v>2154</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="3" t="n">
         <v>1077</v>
       </c>
     </row>
@@ -1213,28 +1225,28 @@
           <t>potassium</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="3" t="n">
+      <c r="B23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="2" t="n">
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="3" t="n">
         <v>656</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K23" s="3" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1244,34 +1256,34 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="4" t="n">
         <v>0.39</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="4" t="n">
         <v>1.51</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="I24" s="5" t="n">
-        <v>0.0007709695396456034</v>
-      </c>
-      <c r="J24" s="2" t="n">
+      <c r="I24" s="6" t="n">
+        <v>0.000770969539645604</v>
+      </c>
+      <c r="J24" s="3" t="n">
         <v>355464</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="3" t="n">
         <v>29777</v>
       </c>
     </row>
@@ -1281,34 +1293,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F25" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="5" t="n">
         <v>85.8</v>
       </c>
-      <c r="I25" s="5" t="n">
-        <v>0.08361480732068774</v>
-      </c>
-      <c r="J25" s="2" t="n">
+      <c r="I25" s="6" t="n">
+        <v>0.08361480732068771</v>
+      </c>
+      <c r="J25" s="3" t="n">
         <v>264478</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="3" t="n">
         <v>15275</v>
       </c>
     </row>
@@ -1318,28 +1330,28 @@
           <t>iodine</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="3" t="n">
+      <c r="B26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="2" t="n">
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="3" t="n">
         <v>656</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K26" s="3" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1349,28 +1361,28 @@
           <t>time_restricted_eating</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="3" t="n">
+      <c r="B27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="2" t="n">
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="3" t="n">
         <v>1455</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K27" s="3" t="n">
         <v>607</v>
       </c>
     </row>
@@ -1380,28 +1392,28 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>0.24</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>2.64</v>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="4" t="n">
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="2" t="n">
+      <c r="I28" s="6" t="inlineStr"/>
+      <c r="J28" s="3" t="n">
         <v>58714</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K28" s="3" t="n">
         <v>851</v>
       </c>
     </row>
@@ -1411,28 +1423,28 @@
           <t>mushrooms</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="3" t="n">
+      <c r="B29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="2" t="n">
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="3" t="n">
         <v>36499</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" s="3" t="n">
         <v>1204</v>
       </c>
     </row>
@@ -1442,34 +1454,34 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="F30" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="5" t="n">
         <v>70.8</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <v>0.001893379785459786</v>
-      </c>
-      <c r="J30" s="2" t="n">
+      <c r="I30" s="6" t="n">
+        <v>0.001893379785459788</v>
+      </c>
+      <c r="J30" s="3" t="n">
         <v>291729</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="K30" s="3" t="n">
         <v>26444</v>
       </c>
     </row>
@@ -1479,34 +1491,34 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F31" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="4" t="n">
         <v>1.71</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="5" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="I31" s="5" t="n">
-        <v>0.2452061889413494</v>
-      </c>
-      <c r="J31" s="2" t="n">
+      <c r="I31" s="6" t="n">
+        <v>0.2452061889413495</v>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>262978</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="K31" s="3" t="n">
         <v>4988</v>
       </c>
     </row>
@@ -1516,34 +1528,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="4" t="n">
         <v>0.51</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="5" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I32" s="6" t="n">
         <v>0.9264859141728312</v>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="J32" s="3" t="n">
         <v>68944</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="K32" s="3" t="n">
         <v>7699</v>
       </c>
     </row>
@@ -1553,28 +1565,28 @@
           <t>fish_oil</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="4" t="n">
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="2" t="n">
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="3" t="n">
         <v>37289</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="K33" s="3" t="n">
         <v>1735</v>
       </c>
     </row>
@@ -1584,34 +1596,34 @@
           <t>legumes</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="5" t="n">
         <v>62.4</v>
       </c>
-      <c r="I34" s="5" t="n">
-        <v>0.006170430008920979</v>
-      </c>
-      <c r="J34" s="2" t="n">
+      <c r="I34" s="6" t="n">
+        <v>0.006170430008920973</v>
+      </c>
+      <c r="J34" s="3" t="n">
         <v>1155076</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="K34" s="3" t="n">
         <v>79072</v>
       </c>
     </row>
@@ -1621,34 +1633,34 @@
           <t>soluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n">
+      <c r="B35" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="H35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>0.1883996373295241</v>
-      </c>
-      <c r="J35" s="2" t="n">
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>0.188399637329524</v>
+      </c>
+      <c r="J35" s="3" t="n">
         <v>80888</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="K35" s="3" t="n">
         <v>10851</v>
       </c>
     </row>
@@ -1658,34 +1670,34 @@
           <t>vitamin_b6</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" s="4" t="n">
         <v>1.41</v>
       </c>
-      <c r="H36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>0.2443574036478494</v>
-      </c>
-      <c r="J36" s="2" t="n">
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>0.2443574036478493</v>
+      </c>
+      <c r="J36" s="3" t="n">
         <v>70879</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K36" s="3" t="n">
         <v>7656</v>
       </c>
     </row>
@@ -1695,28 +1707,28 @@
           <t>plant_based_diet</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="4" t="n">
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="5" t="n">
         <v>39.5</v>
       </c>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="2" t="n">
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="3" t="n">
         <v>211318</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="K37" s="3" t="n">
         <v>24516</v>
       </c>
     </row>
@@ -1726,28 +1738,28 @@
           <t>caffeine</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="3" t="n">
+      <c r="B38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="2" t="n">
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="3" t="n">
         <v>46667</v>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="K38" s="3" t="n">
         <v>3037</v>
       </c>
     </row>
@@ -1757,28 +1769,28 @@
           <t>ginseng</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="3" t="n">
+      <c r="B39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="2" t="n">
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K39" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1788,34 +1800,34 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B40" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="C40" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="E40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="3" t="n">
+      <c r="E40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="G40" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="H40" s="5" t="n">
         <v>42.9</v>
       </c>
-      <c r="I40" s="5" t="n">
+      <c r="I40" s="6" t="n">
         <v>0.07744276379719461</v>
       </c>
-      <c r="J40" s="2" t="n">
+      <c r="J40" s="3" t="n">
         <v>972077</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="K40" s="3" t="n">
         <v>64899</v>
       </c>
     </row>
@@ -1825,34 +1837,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B41" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C41" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="F41" s="4" t="n">
         <v>0.49</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="4" t="n">
         <v>1.77</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="I41" s="5" t="n">
-        <v>0.4656904115016956</v>
-      </c>
-      <c r="J41" s="2" t="n">
+      <c r="I41" s="6" t="n">
+        <v>0.4656904115016954</v>
+      </c>
+      <c r="J41" s="3" t="n">
         <v>121104</v>
       </c>
-      <c r="K41" s="2" t="n">
+      <c r="K41" s="3" t="n">
         <v>7521</v>
       </c>
     </row>
@@ -1862,28 +1874,28 @@
           <t>ginkgo_biloba</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="4" t="n">
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="5" t="n">
         <v>46.8</v>
       </c>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="2" t="n">
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="3" t="n">
         <v>38308</v>
       </c>
-      <c r="K42" s="2" t="n">
+      <c r="K42" s="3" t="n">
         <v>1665</v>
       </c>
     </row>
@@ -1893,34 +1905,34 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B43" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="C43" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="F43" s="3" t="n">
+      <c r="F43" s="4" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="G43" s="4" t="n">
         <v>12.3</v>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="H43" s="5" t="n">
         <v>55.4</v>
       </c>
-      <c r="I43" s="5" t="n">
-        <v>0.6285558694668993</v>
-      </c>
-      <c r="J43" s="2" t="n">
+      <c r="I43" s="6" t="n">
+        <v>0.6285558694668995</v>
+      </c>
+      <c r="J43" s="3" t="n">
         <v>144141</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="K43" s="3" t="n">
         <v>7729</v>
       </c>
     </row>
@@ -1930,34 +1942,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B44" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="C44" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="G44" s="4" t="n">
         <v>1.32</v>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="H44" s="5" t="n">
         <v>75.90000000000001</v>
       </c>
-      <c r="I44" s="5" t="n">
-        <v>0.1015950190265766</v>
-      </c>
-      <c r="J44" s="2" t="n">
+      <c r="I44" s="6" t="n">
+        <v>0.1015950190265765</v>
+      </c>
+      <c r="J44" s="3" t="n">
         <v>404649</v>
       </c>
-      <c r="K44" s="2" t="n">
+      <c r="K44" s="3" t="n">
         <v>36660</v>
       </c>
     </row>
@@ -1967,28 +1979,28 @@
           <t>mediterranean_diet</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="3" t="n">
+      <c r="B45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="2" t="n">
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="3" t="n">
         <v>47867</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="K45" s="3" t="n">
         <v>6220</v>
       </c>
     </row>
@@ -1998,28 +2010,28 @@
           <t>dash_diet</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="3" t="n">
+      <c r="B46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="4" t="n">
         <v>1.04</v>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="2" t="n">
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="3" t="n">
         <v>72784</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="K46" s="3" t="n">
         <v>1408</v>
       </c>
     </row>
@@ -2029,34 +2041,34 @@
           <t>omega_9_fatty_acids</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B47" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C47" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="4" t="n">
         <v>1.47</v>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="F47" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="G47" s="3" t="n">
+      <c r="G47" s="4" t="n">
         <v>83.58</v>
       </c>
-      <c r="H47" s="4" t="n">
+      <c r="H47" s="5" t="n">
         <v>64.7</v>
       </c>
-      <c r="I47" s="5" t="n">
+      <c r="I47" s="6" t="n">
         <v>0.8731289622544238</v>
       </c>
-      <c r="J47" s="2" t="n">
+      <c r="J47" s="3" t="n">
         <v>200953</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="K47" s="3" t="n">
         <v>7887</v>
       </c>
     </row>
@@ -2066,28 +2078,28 @@
           <t>plant_protein_intake</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="3" t="n">
+      <c r="B48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D48" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="2" t="n">
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr"/>
+      <c r="J48" s="3" t="n">
         <v>150671</v>
       </c>
-      <c r="K48" s="2" t="n">
+      <c r="K48" s="3" t="n">
         <v>14238</v>
       </c>
     </row>
@@ -2097,28 +2109,28 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="3" t="n">
+      <c r="B49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="D49" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="2" t="n">
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="3" t="n">
         <v>159482</v>
       </c>
-      <c r="K49" s="2" t="n">
+      <c r="K49" s="3" t="n">
         <v>17349</v>
       </c>
     </row>
@@ -2128,28 +2140,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B50" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="C50" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="D50" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="2" t="n">
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr"/>
+      <c r="J50" s="3" t="n">
         <v>109557</v>
       </c>
-      <c r="K50" s="2" t="n">
+      <c r="K50" s="3" t="n">
         <v>3064</v>
       </c>
     </row>
@@ -2159,34 +2171,34 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n">
+      <c r="B51" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="C51" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="D51" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="F51" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G51" s="3" t="n">
+      <c r="G51" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="H51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="5" t="n">
+      <c r="H51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="6" t="n">
         <v>0.8121269612161565</v>
       </c>
-      <c r="J51" s="2" t="n">
+      <c r="J51" s="3" t="n">
         <v>900752</v>
       </c>
-      <c r="K51" s="2" t="n">
+      <c r="K51" s="3" t="n">
         <v>53381</v>
       </c>
     </row>
@@ -2196,34 +2208,34 @@
           <t>eicosapentaenoic_acid</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B52" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="C52" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="D52" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F52" s="3" t="n">
+      <c r="F52" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="G52" s="3" t="n">
+      <c r="G52" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="H52" s="4" t="n">
+      <c r="H52" s="5" t="n">
         <v>65.2</v>
       </c>
-      <c r="I52" s="5" t="n">
-        <v>0.5746798036256721</v>
-      </c>
-      <c r="J52" s="2" t="n">
+      <c r="I52" s="6" t="n">
+        <v>0.5746798036256722</v>
+      </c>
+      <c r="J52" s="3" t="n">
         <v>444156</v>
       </c>
-      <c r="K52" s="2" t="n">
+      <c r="K52" s="3" t="n">
         <v>13552</v>
       </c>
     </row>
@@ -2233,28 +2245,28 @@
           <t>docosapentaenoic_acid_omega_3</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n">
+      <c r="B53" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="3" t="n">
+      <c r="C53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="2" t="n">
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="3" t="n">
         <v>143344</v>
       </c>
-      <c r="K53" s="2" t="n">
+      <c r="K53" s="3" t="n">
         <v>7412</v>
       </c>
     </row>
@@ -2264,34 +2276,34 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B54" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="3" t="n">
+      <c r="C54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E54" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="F54" s="3" t="n">
+      <c r="F54" s="4" t="n">
         <v>0.18</v>
       </c>
-      <c r="G54" s="3" t="n">
+      <c r="G54" s="4" t="n">
         <v>5.71</v>
       </c>
-      <c r="H54" s="4" t="n">
+      <c r="H54" s="5" t="n">
         <v>84.2</v>
       </c>
-      <c r="I54" s="5" t="n">
+      <c r="I54" s="6" t="n">
         <v>0.9535391069907841</v>
       </c>
-      <c r="J54" s="2" t="n">
+      <c r="J54" s="3" t="n">
         <v>3128</v>
       </c>
-      <c r="K54" s="2" t="n">
+      <c r="K54" s="3" t="n">
         <v>1292</v>
       </c>
     </row>
@@ -2301,28 +2313,28 @@
           <t>gondoic_acid</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="3" t="n">
+      <c r="B55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="D55" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="2" t="n">
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr"/>
+      <c r="J55" s="3" t="n">
         <v>142239</v>
       </c>
-      <c r="K55" s="2" t="n">
+      <c r="K55" s="3" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2332,34 +2344,34 @@
           <t>multivitamin</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="C56" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="D56" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" s="4" t="n">
         <v>1.04</v>
       </c>
-      <c r="F56" s="3" t="n">
+      <c r="F56" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="G56" s="3" t="n">
+      <c r="G56" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="H56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="5" t="n">
+      <c r="H56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
         <v>0.9082727513733182</v>
       </c>
-      <c r="J56" s="2" t="n">
+      <c r="J56" s="3" t="n">
         <v>54340</v>
       </c>
-      <c r="K56" s="2" t="n">
+      <c r="K56" s="3" t="n">
         <v>5633</v>
       </c>
     </row>
@@ -2369,34 +2381,34 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="B57" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="C57" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="D57" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="F57" s="3" t="n">
+      <c r="F57" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="G57" s="3" t="n">
+      <c r="G57" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H57" s="5" t="n">
         <v>74.3</v>
       </c>
-      <c r="I57" s="5" t="n">
-        <v>0.9513120562303944</v>
-      </c>
-      <c r="J57" s="2" t="n">
+      <c r="I57" s="6" t="n">
+        <v>0.9513120562303943</v>
+      </c>
+      <c r="J57" s="3" t="n">
         <v>560815</v>
       </c>
-      <c r="K57" s="2" t="n">
+      <c r="K57" s="3" t="n">
         <v>31749</v>
       </c>
     </row>
@@ -2406,28 +2418,28 @@
           <t>betaine</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" s="3" t="n">
+      <c r="B58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D58" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="2" t="n">
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr"/>
+      <c r="J58" s="3" t="n">
         <v>47896</v>
       </c>
-      <c r="K58" s="2" t="n">
+      <c r="K58" s="3" t="n">
         <v>695</v>
       </c>
     </row>
@@ -2437,34 +2449,34 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n">
+      <c r="B59" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="C59" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D59" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="F59" s="3" t="n">
+      <c r="F59" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="G59" s="3" t="n">
+      <c r="G59" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="H59" s="5" t="n">
         <v>80.8</v>
       </c>
-      <c r="I59" s="5" t="n">
-        <v>0.9371596744819082</v>
-      </c>
-      <c r="J59" s="2" t="n">
+      <c r="I59" s="6" t="n">
+        <v>0.9371596744819083</v>
+      </c>
+      <c r="J59" s="3" t="n">
         <v>568081</v>
       </c>
-      <c r="K59" s="2" t="n">
+      <c r="K59" s="3" t="n">
         <v>36597</v>
       </c>
     </row>
@@ -2474,34 +2486,34 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B60" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="C60" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="D60" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="E60" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F60" s="3" t="n">
+      <c r="F60" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="G60" s="3" t="n">
+      <c r="G60" s="4" t="n">
         <v>1.22</v>
       </c>
-      <c r="H60" s="4" t="n">
+      <c r="H60" s="5" t="n">
         <v>38.1</v>
       </c>
-      <c r="I60" s="5" t="n">
-        <v>0.4142673366090833</v>
-      </c>
-      <c r="J60" s="2" t="n">
+      <c r="I60" s="6" t="n">
+        <v>0.4142673366090839</v>
+      </c>
+      <c r="J60" s="3" t="n">
         <v>248736</v>
       </c>
-      <c r="K60" s="2" t="n">
+      <c r="K60" s="3" t="n">
         <v>13760</v>
       </c>
     </row>
@@ -2511,28 +2523,28 @@
           <t>vitamin_k1</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="3" t="n">
+      <c r="B61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="D61" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="E61" s="4" t="n">
         <v>1.48</v>
       </c>
-      <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="2" t="n">
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="3" t="n">
         <v>11319</v>
       </c>
-      <c r="K61" s="2" t="n">
+      <c r="K61" s="3" t="n">
         <v>268</v>
       </c>
     </row>
@@ -2542,34 +2554,34 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n">
+      <c r="B62" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C62" s="3" t="n">
+      <c r="C62" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="D62" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="E62" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F62" s="3" t="n">
+      <c r="F62" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="G62" s="3" t="n">
+      <c r="G62" s="4" t="n">
         <v>1.26</v>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="H62" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I62" s="5" t="n">
+      <c r="I62" s="6" t="n">
         <v>0.1931737969450245</v>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="J62" s="3" t="n">
         <v>91771</v>
       </c>
-      <c r="K62" s="2" t="n">
+      <c r="K62" s="3" t="n">
         <v>19124</v>
       </c>
     </row>
@@ -2579,28 +2591,28 @@
           <t>saw_palmetto</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" s="3" t="n">
+      <c r="B63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="D63" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="E63" s="4" t="n">
         <v>1.19</v>
       </c>
-      <c r="F63" s="3" t="inlineStr"/>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="2" t="n">
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr"/>
+      <c r="J63" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K63" s="2" t="n">
+      <c r="K63" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2610,28 +2622,28 @@
           <t>chondroitin</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" s="3" t="n">
+      <c r="B64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="D64" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E64" s="3" t="n">
+      <c r="E64" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr"/>
-      <c r="H64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="2" t="n">
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr"/>
+      <c r="J64" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K64" s="2" t="n">
+      <c r="K64" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2641,28 +2653,28 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
+      <c r="B65" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C65" s="3" t="n">
+      <c r="C65" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D65" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="3" t="n">
+      <c r="D65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F65" s="3" t="inlineStr"/>
-      <c r="G65" s="3" t="inlineStr"/>
-      <c r="H65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="2" t="n">
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr"/>
+      <c r="J65" s="3" t="n">
         <v>43360</v>
       </c>
-      <c r="K65" s="2" t="n">
+      <c r="K65" s="3" t="n">
         <v>6174</v>
       </c>
     </row>
@@ -2672,34 +2684,34 @@
           <t>iron</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="C66" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D66" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="E66" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="F66" s="3" t="n">
+      <c r="F66" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="G66" s="3" t="n">
+      <c r="G66" s="4" t="n">
         <v>1.41</v>
       </c>
-      <c r="H66" s="4" t="n">
+      <c r="H66" s="5" t="n">
         <v>77.7</v>
       </c>
-      <c r="I66" s="5" t="n">
-        <v>0.8981574513904265</v>
-      </c>
-      <c r="J66" s="2" t="n">
+      <c r="I66" s="6" t="n">
+        <v>0.8981574513904264</v>
+      </c>
+      <c r="J66" s="3" t="n">
         <v>184031</v>
       </c>
-      <c r="K66" s="2" t="n">
+      <c r="K66" s="3" t="n">
         <v>11578</v>
       </c>
     </row>
@@ -2709,28 +2721,28 @@
           <t>mineral_supplements</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="3" t="n">
+      <c r="B67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D67" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E67" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="2" t="n">
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr"/>
+      <c r="J67" s="3" t="n">
         <v>10011</v>
       </c>
-      <c r="K67" s="2" t="n">
+      <c r="K67" s="3" t="n">
         <v>815</v>
       </c>
     </row>
@@ -2740,34 +2752,34 @@
           <t>glucosamine</t>
         </is>
       </c>
-      <c r="B68" s="2" t="n">
+      <c r="B68" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="C68" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="D68" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="E68" s="3" t="n">
+      <c r="E68" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F68" s="3" t="n">
+      <c r="F68" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="G68" s="3" t="n">
+      <c r="G68" s="4" t="n">
         <v>1.43</v>
       </c>
-      <c r="H68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="5" t="n">
+      <c r="H68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="6" t="n">
         <v>0.01558217739312316</v>
       </c>
-      <c r="J68" s="2" t="n">
+      <c r="J68" s="3" t="n">
         <v>265129</v>
       </c>
-      <c r="K68" s="2" t="n">
+      <c r="K68" s="3" t="n">
         <v>16136</v>
       </c>
     </row>
@@ -2777,28 +2789,28 @@
           <t>magnesium</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n">
+      <c r="B69" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="C69" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="D69" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="E69" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F69" s="3" t="inlineStr"/>
-      <c r="G69" s="3" t="inlineStr"/>
-      <c r="H69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="2" t="n">
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
+      <c r="H69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr"/>
+      <c r="J69" s="3" t="n">
         <v>43795</v>
       </c>
-      <c r="K69" s="2" t="n">
+      <c r="K69" s="3" t="n">
         <v>6400</v>
       </c>
     </row>
@@ -2808,34 +2820,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="C70" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D70" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="E70" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="F70" s="3" t="n">
+      <c r="F70" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="G70" s="3" t="n">
+      <c r="G70" s="4" t="n">
         <v>1.29</v>
       </c>
-      <c r="H70" s="4" t="n">
+      <c r="H70" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="I70" s="5" t="n">
-        <v>0.0241544633916244</v>
-      </c>
-      <c r="J70" s="2" t="n">
+      <c r="I70" s="6" t="n">
+        <v>0.02415446339162438</v>
+      </c>
+      <c r="J70" s="3" t="n">
         <v>1089615</v>
       </c>
-      <c r="K70" s="2" t="n">
+      <c r="K70" s="3" t="n">
         <v>64702</v>
       </c>
     </row>
@@ -2845,28 +2857,28 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" s="3" t="n">
+      <c r="B71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="D71" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E71" s="3" t="n">
+      <c r="E71" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="F71" s="3" t="inlineStr"/>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="2" t="n">
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
+      <c r="H71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr"/>
+      <c r="J71" s="3" t="n">
         <v>21533</v>
       </c>
-      <c r="K71" s="2" t="n">
+      <c r="K71" s="3" t="n">
         <v>291</v>
       </c>
     </row>
@@ -2876,28 +2888,28 @@
           <t>vitamin_b2</t>
         </is>
       </c>
-      <c r="B72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="3" t="n">
+      <c r="B72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="D72" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="3" t="n">
+      <c r="D72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="F72" s="3" t="inlineStr"/>
-      <c r="G72" s="3" t="inlineStr"/>
-      <c r="H72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="2" t="n">
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr"/>
+      <c r="J72" s="3" t="n">
         <v>1595</v>
       </c>
-      <c r="K72" s="2" t="n">
+      <c r="K72" s="3" t="n">
         <v>561</v>
       </c>
     </row>
@@ -2907,34 +2919,34 @@
           <t>whole_grain_intake</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C73" s="3" t="n">
+      <c r="C73" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="D73" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="E73" s="3" t="n">
+      <c r="E73" s="4" t="n">
         <v>1.26</v>
       </c>
-      <c r="F73" s="3" t="n">
+      <c r="F73" s="4" t="n">
         <v>0.24</v>
       </c>
-      <c r="G73" s="3" t="n">
+      <c r="G73" s="4" t="n">
         <v>5.08</v>
       </c>
-      <c r="H73" s="4" t="n">
+      <c r="H73" s="5" t="n">
         <v>83.3</v>
       </c>
-      <c r="I73" s="5" t="n">
+      <c r="I73" s="6" t="n">
         <v>0.1158775811071888</v>
       </c>
-      <c r="J73" s="2" t="n">
+      <c r="J73" s="3" t="n">
         <v>79458</v>
       </c>
-      <c r="K73" s="2" t="n">
+      <c r="K73" s="3" t="n">
         <v>7209</v>
       </c>
     </row>
@@ -2944,28 +2956,28 @@
           <t>phosphorus</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C74" s="3" t="n">
+      <c r="B74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="D74" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="E74" s="3" t="n">
+      <c r="E74" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="F74" s="3" t="inlineStr"/>
-      <c r="G74" s="3" t="inlineStr"/>
-      <c r="H74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="5" t="inlineStr"/>
-      <c r="J74" s="2" t="n">
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr"/>
+      <c r="H74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr"/>
+      <c r="J74" s="3" t="n">
         <v>47885</v>
       </c>
-      <c r="K74" s="2" t="n">
+      <c r="K74" s="3" t="n">
         <v>5861</v>
       </c>
     </row>
@@ -2975,34 +2987,34 @@
           <t>vitamin_b12</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B75" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C75" s="3" t="n">
+      <c r="C75" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="D75" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="E75" s="3" t="n">
+      <c r="E75" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="F75" s="3" t="n">
+      <c r="F75" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="G75" s="3" t="n">
+      <c r="G75" s="4" t="n">
         <v>1.71</v>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="H75" s="5" t="n">
         <v>64.5</v>
       </c>
-      <c r="I75" s="5" t="n">
-        <v>0.01145019300160749</v>
-      </c>
-      <c r="J75" s="2" t="n">
+      <c r="I75" s="6" t="n">
+        <v>0.0114501930016075</v>
+      </c>
+      <c r="J75" s="3" t="n">
         <v>5961</v>
       </c>
-      <c r="K75" s="2" t="n">
+      <c r="K75" s="3" t="n">
         <v>2681</v>
       </c>
     </row>
@@ -3012,34 +3024,34 @@
           <t>zinc</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n">
+      <c r="B76" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C76" s="3" t="n">
+      <c r="C76" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="D76" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="E76" s="3" t="n">
+      <c r="E76" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="F76" s="3" t="n">
+      <c r="F76" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="G76" s="3" t="n">
+      <c r="G76" s="4" t="n">
         <v>3.01</v>
       </c>
-      <c r="H76" s="4" t="n">
+      <c r="H76" s="5" t="n">
         <v>80.5</v>
       </c>
-      <c r="I76" s="5" t="n">
-        <v>0.5211814544747841</v>
-      </c>
-      <c r="J76" s="2" t="n">
+      <c r="I76" s="6" t="n">
+        <v>0.5211814544747839</v>
+      </c>
+      <c r="J76" s="3" t="n">
         <v>49478</v>
       </c>
-      <c r="K76" s="2" t="n">
+      <c r="K76" s="3" t="n">
         <v>6840</v>
       </c>
     </row>
@@ -3049,34 +3061,34 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n">
+      <c r="B77" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="C77" s="4" t="n">
         <v>1.14</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D77" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="E77" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="F77" s="3" t="n">
+      <c r="F77" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="G77" s="3" t="n">
+      <c r="G77" s="4" t="n">
         <v>1.53</v>
       </c>
-      <c r="H77" s="4" t="n">
+      <c r="H77" s="5" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="I77" s="5" t="n">
-        <v>0.04932265398703134</v>
-      </c>
-      <c r="J77" s="2" t="n">
+      <c r="I77" s="6" t="n">
+        <v>0.04932265398703133</v>
+      </c>
+      <c r="J77" s="3" t="n">
         <v>951593</v>
       </c>
-      <c r="K77" s="2" t="n">
+      <c r="K77" s="3" t="n">
         <v>55176</v>
       </c>
     </row>
@@ -3086,34 +3098,34 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n">
+      <c r="B78" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C78" s="3" t="n">
+      <c r="C78" s="4" t="n">
         <v>1.14</v>
       </c>
-      <c r="D78" s="3" t="n">
+      <c r="D78" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="E78" s="3" t="n">
+      <c r="E78" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="F78" s="3" t="n">
+      <c r="F78" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="G78" s="3" t="n">
+      <c r="G78" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="H78" s="4" t="n">
+      <c r="H78" s="5" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="I78" s="5" t="n">
-        <v>0.01640873960670475</v>
-      </c>
-      <c r="J78" s="2" t="n">
+      <c r="I78" s="6" t="n">
+        <v>0.01640873960670477</v>
+      </c>
+      <c r="J78" s="3" t="n">
         <v>547664</v>
       </c>
-      <c r="K78" s="2" t="n">
+      <c r="K78" s="3" t="n">
         <v>63207</v>
       </c>
     </row>
@@ -3123,34 +3135,34 @@
           <t>alpha_linolenic_acid</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n">
+      <c r="B79" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C79" s="3" t="n">
+      <c r="C79" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="D79" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="E79" s="3" t="n">
+      <c r="E79" s="4" t="n">
         <v>1.43</v>
       </c>
-      <c r="F79" s="3" t="n">
+      <c r="F79" s="4" t="n">
         <v>0.58</v>
       </c>
-      <c r="G79" s="3" t="n">
+      <c r="G79" s="4" t="n">
         <v>2.27</v>
       </c>
-      <c r="H79" s="4" t="n">
+      <c r="H79" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="I79" s="5" t="n">
-        <v>0.2932566086946222</v>
-      </c>
-      <c r="J79" s="2" t="n">
+      <c r="I79" s="6" t="n">
+        <v>0.2932566086946219</v>
+      </c>
+      <c r="J79" s="3" t="n">
         <v>173827</v>
       </c>
-      <c r="K79" s="2" t="n">
+      <c r="K79" s="3" t="n">
         <v>9647</v>
       </c>
     </row>
@@ -3160,34 +3172,34 @@
           <t>antioxidants</t>
         </is>
       </c>
-      <c r="B80" s="2" t="n">
+      <c r="B80" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C80" s="3" t="n">
+      <c r="C80" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="D80" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="E80" s="3" t="n">
+      <c r="E80" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="F80" s="3" t="n">
+      <c r="F80" s="4" t="n">
         <v>0.04</v>
       </c>
-      <c r="G80" s="3" t="n">
+      <c r="G80" s="4" t="n">
         <v>33.17</v>
       </c>
-      <c r="H80" s="4" t="n">
+      <c r="H80" s="5" t="n">
         <v>90.3</v>
       </c>
-      <c r="I80" s="5" t="n">
+      <c r="I80" s="6" t="n">
         <v>0.1648989938761477</v>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="J80" s="3" t="n">
         <v>56601</v>
       </c>
-      <c r="K80" s="2" t="n">
+      <c r="K80" s="3" t="n">
         <v>7271</v>
       </c>
     </row>
@@ -3197,34 +3209,34 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B81" s="2" t="n">
+      <c r="B81" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C81" s="3" t="n">
+      <c r="C81" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="D81" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="E81" s="4" t="n">
         <v>1.42</v>
       </c>
-      <c r="F81" s="3" t="n">
+      <c r="F81" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="G81" s="3" t="n">
+      <c r="G81" s="4" t="n">
         <v>2.43</v>
       </c>
-      <c r="H81" s="4" t="n">
+      <c r="H81" s="5" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="I81" s="5" t="n">
+      <c r="I81" s="6" t="n">
         <v>0.9490649069662661</v>
       </c>
-      <c r="J81" s="2" t="n">
+      <c r="J81" s="3" t="n">
         <v>70012</v>
       </c>
-      <c r="K81" s="2" t="n">
+      <c r="K81" s="3" t="n">
         <v>17837</v>
       </c>
     </row>
@@ -3234,28 +3246,28 @@
           <t>choline</t>
         </is>
       </c>
-      <c r="B82" s="2" t="n">
+      <c r="B82" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C82" s="3" t="n">
+      <c r="C82" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="D82" s="3" t="n">
+      <c r="D82" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="E82" s="3" t="n">
+      <c r="E82" s="4" t="n">
         <v>1.67</v>
       </c>
-      <c r="F82" s="3" t="inlineStr"/>
-      <c r="G82" s="3" t="inlineStr"/>
-      <c r="H82" s="4" t="n">
+      <c r="F82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr"/>
+      <c r="H82" s="5" t="n">
         <v>71.2</v>
       </c>
-      <c r="I82" s="5" t="inlineStr"/>
-      <c r="J82" s="2" t="n">
+      <c r="I82" s="6" t="inlineStr"/>
+      <c r="J82" s="3" t="n">
         <v>8123</v>
       </c>
-      <c r="K82" s="2" t="n">
+      <c r="K82" s="3" t="n">
         <v>1372</v>
       </c>
     </row>
@@ -3265,34 +3277,34 @@
           <t>coenzyme_q10</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n">
+      <c r="B83" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C83" s="3" t="n">
+      <c r="C83" s="4" t="n">
         <v>1.19</v>
       </c>
-      <c r="D83" s="3" t="n">
+      <c r="D83" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E83" s="3" t="n">
+      <c r="E83" s="4" t="n">
         <v>1.79</v>
       </c>
-      <c r="F83" s="3" t="n">
+      <c r="F83" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="G83" s="3" t="n">
+      <c r="G83" s="4" t="n">
         <v>119.97</v>
       </c>
-      <c r="H83" s="4" t="n">
+      <c r="H83" s="5" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="I83" s="5" t="n">
-        <v>0.3692661628018609</v>
-      </c>
-      <c r="J83" s="2" t="n">
+      <c r="I83" s="6" t="n">
+        <v>0.3692661628018608</v>
+      </c>
+      <c r="J83" s="3" t="n">
         <v>36416</v>
       </c>
-      <c r="K83" s="2" t="n">
+      <c r="K83" s="3" t="n">
         <v>2065</v>
       </c>
     </row>
@@ -3302,34 +3314,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B84" s="2" t="n">
+      <c r="B84" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C84" s="3" t="n">
+      <c r="C84" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="D84" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="E84" s="3" t="n">
+      <c r="E84" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="F84" s="3" t="n">
+      <c r="F84" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="G84" s="3" t="n">
+      <c r="G84" s="4" t="n">
         <v>1.66</v>
       </c>
-      <c r="H84" s="4" t="n">
+      <c r="H84" s="5" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="I84" s="5" t="n">
-        <v>0.00522361300352628</v>
-      </c>
-      <c r="J84" s="2" t="n">
+      <c r="I84" s="6" t="n">
+        <v>0.005223613003526282</v>
+      </c>
+      <c r="J84" s="3" t="n">
         <v>1911711</v>
       </c>
-      <c r="K84" s="2" t="n">
+      <c r="K84" s="3" t="n">
         <v>47035</v>
       </c>
     </row>
@@ -3339,34 +3351,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B85" s="2" t="n">
+      <c r="B85" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C85" s="3" t="n">
+      <c r="C85" s="4" t="n">
         <v>1.22</v>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D85" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="E85" s="4" t="n">
         <v>1.34</v>
       </c>
-      <c r="F85" s="3" t="n">
+      <c r="F85" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="G85" s="3" t="n">
+      <c r="G85" s="4" t="n">
         <v>1.79</v>
       </c>
-      <c r="H85" s="4" t="n">
+      <c r="H85" s="5" t="n">
         <v>83.3</v>
       </c>
-      <c r="I85" s="5" t="n">
-        <v>0.1182255463777411</v>
-      </c>
-      <c r="J85" s="2" t="n">
+      <c r="I85" s="6" t="n">
+        <v>0.118225546377741</v>
+      </c>
+      <c r="J85" s="3" t="n">
         <v>688143</v>
       </c>
-      <c r="K85" s="2" t="n">
+      <c r="K85" s="3" t="n">
         <v>33749</v>
       </c>
     </row>
@@ -3376,28 +3388,28 @@
           <t>glutamine</t>
         </is>
       </c>
-      <c r="B86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="3" t="n">
+      <c r="B86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="D86" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="3" t="n">
+      <c r="D86" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="F86" s="3" t="inlineStr"/>
-      <c r="G86" s="3" t="inlineStr"/>
-      <c r="H86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="5" t="inlineStr"/>
-      <c r="J86" s="2" t="n">
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr"/>
+      <c r="J86" s="3" t="n">
         <v>342</v>
       </c>
-      <c r="K86" s="2" t="n">
+      <c r="K86" s="3" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3407,34 +3419,34 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B87" s="2" t="n">
+      <c r="B87" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C87" s="3" t="n">
+      <c r="C87" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="D87" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="3" t="n">
+      <c r="D87" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="F87" s="3" t="n">
+      <c r="F87" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="G87" s="3" t="n">
+      <c r="G87" s="4" t="n">
         <v>12.86</v>
       </c>
-      <c r="H87" s="4" t="n">
+      <c r="H87" s="5" t="n">
         <v>50.3</v>
       </c>
-      <c r="I87" s="5" t="n">
+      <c r="I87" s="6" t="n">
         <v>0.257220017732754</v>
       </c>
-      <c r="J87" s="2" t="n">
+      <c r="J87" s="3" t="n">
         <v>201324</v>
       </c>
-      <c r="K87" s="2" t="n">
+      <c r="K87" s="3" t="n">
         <v>7680</v>
       </c>
     </row>
@@ -3444,34 +3456,34 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B88" s="2" t="n">
+      <c r="B88" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C88" s="3" t="n">
+      <c r="C88" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="D88" s="3" t="n">
+      <c r="D88" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="E88" s="3" t="n">
+      <c r="E88" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="F88" s="3" t="n">
+      <c r="F88" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="G88" s="3" t="n">
+      <c r="G88" s="4" t="n">
         <v>2.04</v>
       </c>
-      <c r="H88" s="4" t="n">
+      <c r="H88" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="I88" s="5" t="n">
-        <v>0.08453464596581806</v>
-      </c>
-      <c r="J88" s="2" t="n">
+      <c r="I88" s="6" t="n">
+        <v>0.084534645965818</v>
+      </c>
+      <c r="J88" s="3" t="n">
         <v>255534</v>
       </c>
-      <c r="K88" s="2" t="n">
+      <c r="K88" s="3" t="n">
         <v>13888</v>
       </c>
     </row>
@@ -3481,28 +3493,28 @@
           <t>creatine</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C89" s="3" t="n">
+      <c r="B89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="D89" s="3" t="n">
+      <c r="D89" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="E89" s="3" t="n">
+      <c r="E89" s="4" t="n">
         <v>1.63</v>
       </c>
-      <c r="F89" s="3" t="inlineStr"/>
-      <c r="G89" s="3" t="inlineStr"/>
-      <c r="H89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="5" t="inlineStr"/>
-      <c r="J89" s="2" t="n">
+      <c r="F89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr"/>
+      <c r="H89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr"/>
+      <c r="J89" s="3" t="n">
         <v>342</v>
       </c>
-      <c r="K89" s="2" t="n">
+      <c r="K89" s="3" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3512,28 +3524,28 @@
           <t>l_valine</t>
         </is>
       </c>
-      <c r="B90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" s="3" t="n">
+      <c r="B90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="D90" s="3" t="n">
+      <c r="D90" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="E90" s="3" t="n">
+      <c r="E90" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="F90" s="3" t="inlineStr"/>
-      <c r="G90" s="3" t="inlineStr"/>
-      <c r="H90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="5" t="inlineStr"/>
-      <c r="J90" s="2" t="n">
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr"/>
+      <c r="H90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr"/>
+      <c r="J90" s="3" t="n">
         <v>342</v>
       </c>
-      <c r="K90" s="2" t="n">
+      <c r="K90" s="3" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3543,28 +3555,28 @@
           <t>l_tyrosine</t>
         </is>
       </c>
-      <c r="B91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" s="3" t="n">
+      <c r="B91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="D91" s="3" t="n">
+      <c r="D91" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="E91" s="3" t="n">
+      <c r="E91" s="4" t="n">
         <v>1.66</v>
       </c>
-      <c r="F91" s="3" t="inlineStr"/>
-      <c r="G91" s="3" t="inlineStr"/>
-      <c r="H91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="2" t="n">
+      <c r="F91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr"/>
+      <c r="H91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr"/>
+      <c r="J91" s="3" t="n">
         <v>342</v>
       </c>
-      <c r="K91" s="2" t="n">
+      <c r="K91" s="3" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3574,28 +3586,28 @@
           <t>chocolate</t>
         </is>
       </c>
-      <c r="B92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" s="3" t="n">
+      <c r="B92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="D92" s="3" t="n">
+      <c r="D92" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="E92" s="3" t="n">
+      <c r="E92" s="4" t="n">
         <v>1.64</v>
       </c>
-      <c r="F92" s="3" t="inlineStr"/>
-      <c r="G92" s="3" t="inlineStr"/>
-      <c r="H92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="5" t="inlineStr"/>
-      <c r="J92" s="2" t="n">
+      <c r="F92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr"/>
+      <c r="H92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr"/>
+      <c r="J92" s="3" t="n">
         <v>2611</v>
       </c>
-      <c r="K92" s="2" t="n">
+      <c r="K92" s="3" t="n">
         <v>1499</v>
       </c>
     </row>
@@ -3605,28 +3617,28 @@
           <t>western_pattern_diet</t>
         </is>
       </c>
-      <c r="B93" s="2" t="n">
+      <c r="B93" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C93" s="3" t="n">
+      <c r="C93" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="D93" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="3" t="n">
+      <c r="D93" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="4" t="n">
         <v>1.82</v>
       </c>
-      <c r="F93" s="3" t="inlineStr"/>
-      <c r="G93" s="3" t="inlineStr"/>
-      <c r="H93" s="4" t="n">
+      <c r="F93" s="4" t="inlineStr"/>
+      <c r="G93" s="4" t="inlineStr"/>
+      <c r="H93" s="5" t="n">
         <v>57.1</v>
       </c>
-      <c r="I93" s="5" t="inlineStr"/>
-      <c r="J93" s="2" t="n">
+      <c r="I93" s="6" t="inlineStr"/>
+      <c r="J93" s="3" t="n">
         <v>44462</v>
       </c>
-      <c r="K93" s="2" t="n">
+      <c r="K93" s="3" t="n">
         <v>1702</v>
       </c>
     </row>
@@ -3636,34 +3648,34 @@
           <t>fermented_foods</t>
         </is>
       </c>
-      <c r="B94" s="2" t="n">
+      <c r="B94" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C94" s="3" t="n">
+      <c r="C94" s="4" t="n">
         <v>1.37</v>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="D94" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="E94" s="3" t="n">
+      <c r="E94" s="4" t="n">
         <v>2.45</v>
       </c>
-      <c r="F94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3" t="n">
+      <c r="F94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="4" t="n">
         <v>664.3099999999999</v>
       </c>
-      <c r="H94" s="4" t="n">
+      <c r="H94" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="I94" s="5" t="n">
+      <c r="I94" s="6" t="n">
         <v>0.1814798483236068</v>
       </c>
-      <c r="J94" s="2" t="n">
+      <c r="J94" s="3" t="n">
         <v>3460</v>
       </c>
-      <c r="K94" s="2" t="n">
+      <c r="K94" s="3" t="n">
         <v>339</v>
       </c>
     </row>
@@ -3673,28 +3685,28 @@
           <t>gamma_linolenic_acid</t>
         </is>
       </c>
-      <c r="B95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" s="3" t="n">
+      <c r="B95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="4" t="n">
         <v>1.41</v>
       </c>
-      <c r="D95" s="3" t="n">
+      <c r="D95" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E95" s="3" t="n">
+      <c r="E95" s="4" t="n">
         <v>2.12</v>
       </c>
-      <c r="F95" s="3" t="inlineStr"/>
-      <c r="G95" s="3" t="inlineStr"/>
-      <c r="H95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="5" t="inlineStr"/>
-      <c r="J95" s="2" t="n">
+      <c r="F95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr"/>
+      <c r="H95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr"/>
+      <c r="J95" s="3" t="n">
         <v>952</v>
       </c>
-      <c r="K95" s="2" t="n">
+      <c r="K95" s="3" t="n">
         <v>476</v>
       </c>
     </row>
@@ -3704,28 +3716,28 @@
           <t>dihomo_gamma_linolenic_acid</t>
         </is>
       </c>
-      <c r="B96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" s="3" t="n">
+      <c r="B96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="D96" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="E96" s="3" t="n">
+      <c r="E96" s="4" t="n">
         <v>2.3</v>
       </c>
-      <c r="F96" s="3" t="inlineStr"/>
-      <c r="G96" s="3" t="inlineStr"/>
-      <c r="H96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="5" t="inlineStr"/>
-      <c r="J96" s="2" t="n">
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr"/>
+      <c r="J96" s="3" t="n">
         <v>952</v>
       </c>
-      <c r="K96" s="2" t="n">
+      <c r="K96" s="3" t="n">
         <v>476</v>
       </c>
     </row>
@@ -3735,34 +3747,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B97" s="2" t="n">
+      <c r="B97" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C97" s="3" t="n">
+      <c r="C97" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="D97" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="E97" s="3" t="n">
+      <c r="E97" s="4" t="n">
         <v>2.23</v>
       </c>
-      <c r="F97" s="3" t="n">
+      <c r="F97" s="4" t="n">
         <v>0.49</v>
       </c>
-      <c r="G97" s="3" t="n">
+      <c r="G97" s="4" t="n">
         <v>5.24</v>
       </c>
-      <c r="H97" s="4" t="n">
+      <c r="H97" s="5" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="I97" s="5" t="n">
-        <v>0.081214709783867</v>
-      </c>
-      <c r="J97" s="2" t="n">
+      <c r="I97" s="6" t="n">
+        <v>0.08121470978386684</v>
+      </c>
+      <c r="J97" s="3" t="n">
         <v>873126</v>
       </c>
-      <c r="K97" s="2" t="n">
+      <c r="K97" s="3" t="n">
         <v>56254</v>
       </c>
     </row>
@@ -3772,28 +3784,28 @@
           <t>phosphatidylcholine</t>
         </is>
       </c>
-      <c r="B98" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" s="3" t="n">
+      <c r="B98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" s="4" t="n">
         <v>1.78</v>
       </c>
-      <c r="D98" s="3" t="n">
+      <c r="D98" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="E98" s="3" t="n">
+      <c r="E98" s="4" t="n">
         <v>2.87</v>
       </c>
-      <c r="F98" s="3" t="inlineStr"/>
-      <c r="G98" s="3" t="inlineStr"/>
-      <c r="H98" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="5" t="inlineStr"/>
-      <c r="J98" s="2" t="n">
+      <c r="F98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr"/>
+      <c r="H98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr"/>
+      <c r="J98" s="3" t="n">
         <v>310</v>
       </c>
-      <c r="K98" s="2" t="n">
+      <c r="K98" s="3" t="n">
         <v>41</v>
       </c>
     </row>
@@ -3803,28 +3815,28 @@
           <t>glycine</t>
         </is>
       </c>
-      <c r="B99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C99" s="3" t="n">
+      <c r="B99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="4" t="n">
         <v>1.84</v>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="D99" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="E99" s="3" t="n">
+      <c r="E99" s="4" t="n">
         <v>2.72</v>
       </c>
-      <c r="F99" s="3" t="inlineStr"/>
-      <c r="G99" s="3" t="inlineStr"/>
-      <c r="H99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="5" t="inlineStr"/>
-      <c r="J99" s="2" t="n">
+      <c r="F99" s="4" t="inlineStr"/>
+      <c r="G99" s="4" t="inlineStr"/>
+      <c r="H99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr"/>
+      <c r="J99" s="3" t="n">
         <v>666</v>
       </c>
-      <c r="K99" s="2" t="n">
+      <c r="K99" s="3" t="n">
         <v>333</v>
       </c>
     </row>
@@ -3834,28 +3846,28 @@
           <t>pickled_vegetables</t>
         </is>
       </c>
-      <c r="B100" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C100" s="3" t="n">
+      <c r="B100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="D100" s="3" t="n">
+      <c r="D100" s="4" t="n">
         <v>2.97</v>
       </c>
-      <c r="E100" s="3" t="n">
+      <c r="E100" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="F100" s="3" t="inlineStr"/>
-      <c r="G100" s="3" t="inlineStr"/>
-      <c r="H100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="5" t="inlineStr"/>
-      <c r="J100" s="2" t="n">
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr"/>
+      <c r="H100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr"/>
+      <c r="J100" s="3" t="n">
         <v>404</v>
       </c>
-      <c r="K100" s="2" t="n">
+      <c r="K100" s="3" t="n">
         <v>130</v>
       </c>
     </row>

--- a/summary/yes/exposures_meta_analysis_prostate_cancer_excluding_aggressive_combined.xlsx
+++ b/summary/yes/exposures_meta_analysis_prostate_cancer_excluding_aggressive_combined.xlsx
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,22 +57,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,57 +452,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -526,28 +514,28 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0.03</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="3" t="n">
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>102</v>
       </c>
     </row>
@@ -557,28 +545,28 @@
           <t>natto</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.28</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="3" t="n">
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>140</v>
       </c>
     </row>
@@ -588,28 +576,28 @@
           <t>papaya</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="3" t="n">
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>35</v>
       </c>
     </row>
@@ -619,28 +607,28 @@
           <t>early_time_restricted_eating</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="3" t="n">
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
         <v>1455</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>607</v>
       </c>
     </row>
@@ -650,34 +638,34 @@
           <t>soy</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.41</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="3" t="n">
         <v>2.09</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="4" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="I6" s="6" t="n">
-        <v>0.1010785350953813</v>
-      </c>
-      <c r="J6" s="3" t="n">
+      <c r="I6" s="5" t="n">
+        <v>0.1010785350953814</v>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>85059</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>5399</v>
       </c>
     </row>
@@ -687,28 +675,28 @@
           <t>low_fat_diet</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="n">
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.33</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="3" t="n">
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="2" t="n">
         <v>1170</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>390</v>
       </c>
     </row>
@@ -718,34 +706,34 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="4" t="n">
         <v>76.2</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="5" t="n">
         <v>0.2620449311218541</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" s="2" t="n">
         <v>49170</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>1463</v>
       </c>
     </row>
@@ -755,28 +743,28 @@
           <t>vitamin_k2</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.39</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="3" t="n">
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="2" t="n">
         <v>11319</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="2" t="n">
         <v>268</v>
       </c>
     </row>
@@ -786,34 +774,34 @@
           <t>genistein</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="3" t="n">
         <v>0.66</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.52</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="4" t="n">
         <v>50.6</v>
       </c>
-      <c r="I10" s="6" t="n">
-        <v>0.001566293494770549</v>
-      </c>
-      <c r="J10" s="3" t="n">
+      <c r="I10" s="5" t="n">
+        <v>0.001566293494770547</v>
+      </c>
+      <c r="J10" s="2" t="n">
         <v>64298</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>3531</v>
       </c>
     </row>
@@ -823,34 +811,34 @@
           <t>zeaxanthin</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="3" t="n">
         <v>0.66</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="3" t="n">
         <v>0.09</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="3" t="n">
         <v>4.89</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="4" t="n">
         <v>62.9</v>
       </c>
-      <c r="I11" s="6" t="n">
-        <v>0.8236639670954942</v>
-      </c>
-      <c r="J11" s="3" t="n">
+      <c r="I11" s="5" t="n">
+        <v>0.8236639670954935</v>
+      </c>
+      <c r="J11" s="2" t="n">
         <v>2106</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="2" t="n">
         <v>808</v>
       </c>
     </row>
@@ -860,28 +848,28 @@
           <t>quercetin</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="n">
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="3" t="n">
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
         <v>971</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="2" t="n">
         <v>433</v>
       </c>
     </row>
@@ -891,28 +879,28 @@
           <t>vegan_diet</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="4" t="n">
+      <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="3" t="n">
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
         <v>26346</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="2" t="n">
         <v>1079</v>
       </c>
     </row>
@@ -922,28 +910,28 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="3" t="n">
         <v>0.38</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="5" t="n">
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="n">
         <v>80.7</v>
       </c>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="3" t="n">
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="2" t="n">
         <v>57649</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="2" t="n">
         <v>6553</v>
       </c>
     </row>
@@ -953,28 +941,28 @@
           <t>pyruvate</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4" t="n">
+      <c r="B15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="3" t="n">
         <v>0.52</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="3" t="n">
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="2" t="n">
         <v>666</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="2" t="n">
         <v>333</v>
       </c>
     </row>
@@ -984,34 +972,34 @@
           <t>garlic</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="n">
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>265.07</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="5" t="n">
         <v>0.2044018200861738</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="J16" s="2" t="n">
         <v>36604</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="2" t="n">
         <v>2168</v>
       </c>
     </row>
@@ -1021,28 +1009,28 @@
           <t>vegetarian_diet</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="n">
+      <c r="B17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="3" t="n">
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="2" t="n">
         <v>217937</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="2" t="n">
         <v>9501</v>
       </c>
     </row>
@@ -1052,34 +1040,34 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="3" t="n">
         <v>0.26</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H18" s="4" t="n">
         <v>70.5</v>
       </c>
-      <c r="I18" s="6" t="n">
-        <v>0.4789848163683069</v>
-      </c>
-      <c r="J18" s="3" t="n">
+      <c r="I18" s="5" t="n">
+        <v>0.4789848163683078</v>
+      </c>
+      <c r="J18" s="2" t="n">
         <v>8735</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="2" t="n">
         <v>3057</v>
       </c>
     </row>
@@ -1089,28 +1077,28 @@
           <t>vitamin_k</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="3" t="n">
         <v>0.73</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="3" t="n">
         <v>0.58</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="3" t="n">
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="2" t="n">
         <v>12063</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="2" t="n">
         <v>518</v>
       </c>
     </row>
@@ -1120,34 +1108,34 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H20" s="4" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="I20" s="6" t="n">
-        <v>2.045420729252859e-05</v>
-      </c>
-      <c r="J20" s="3" t="n">
+      <c r="I20" s="5" t="n">
+        <v>2.045420729252854e-05</v>
+      </c>
+      <c r="J20" s="2" t="n">
         <v>1057923</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="2" t="n">
         <v>67108</v>
       </c>
     </row>
@@ -1157,34 +1145,34 @@
           <t>melatonin</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>196.29</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="I21" s="6" t="n">
-        <v>0.0645864721910966</v>
-      </c>
-      <c r="J21" s="3" t="n">
+      <c r="I21" s="5" t="n">
+        <v>0.06458647219109648</v>
+      </c>
+      <c r="J21" s="2" t="n">
         <v>4618</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="2" t="n">
         <v>1414</v>
       </c>
     </row>
@@ -1194,28 +1182,28 @@
           <t>citrulline</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="n">
+      <c r="B22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="3" t="n">
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
         <v>2154</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="2" t="n">
         <v>1077</v>
       </c>
     </row>
@@ -1225,28 +1213,28 @@
           <t>potassium</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="4" t="n">
+      <c r="B23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr"/>
-      <c r="J23" s="3" t="n">
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="2" t="n">
         <v>656</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="2" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1256,34 +1244,34 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="3" t="n">
         <v>0.39</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H24" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="I24" s="6" t="n">
-        <v>0.000770969539645604</v>
-      </c>
-      <c r="J24" s="3" t="n">
+      <c r="I24" s="5" t="n">
+        <v>0.0007709695396456014</v>
+      </c>
+      <c r="J24" s="2" t="n">
         <v>355464</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="2" t="n">
         <v>29777</v>
       </c>
     </row>
@@ -1293,34 +1281,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="H25" s="4" t="n">
         <v>85.8</v>
       </c>
-      <c r="I25" s="6" t="n">
-        <v>0.08361480732068771</v>
-      </c>
-      <c r="J25" s="3" t="n">
+      <c r="I25" s="5" t="n">
+        <v>0.08361480732068802</v>
+      </c>
+      <c r="J25" s="2" t="n">
         <v>264478</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="2" t="n">
         <v>15275</v>
       </c>
     </row>
@@ -1330,28 +1318,28 @@
           <t>iodine</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="4" t="n">
+      <c r="B26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="3" t="n">
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="2" t="n">
         <v>656</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="2" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1361,28 +1349,28 @@
           <t>time_restricted_eating</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="n">
+      <c r="B27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="3" t="n">
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
         <v>1455</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="2" t="n">
         <v>607</v>
       </c>
     </row>
@@ -1392,28 +1380,28 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="3" t="n">
         <v>2.64</v>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="5" t="n">
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="I28" s="6" t="inlineStr"/>
-      <c r="J28" s="3" t="n">
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="2" t="n">
         <v>58714</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="2" t="n">
         <v>851</v>
       </c>
     </row>
@@ -1423,28 +1411,28 @@
           <t>mushrooms</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="4" t="n">
+      <c r="B29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr"/>
-      <c r="J29" s="3" t="n">
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="2" t="n">
         <v>36499</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="2" t="n">
         <v>1204</v>
       </c>
     </row>
@@ -1454,34 +1442,34 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H30" s="4" t="n">
         <v>70.8</v>
       </c>
-      <c r="I30" s="6" t="n">
-        <v>0.001893379785459788</v>
-      </c>
-      <c r="J30" s="3" t="n">
+      <c r="I30" s="5" t="n">
+        <v>0.001893379785459787</v>
+      </c>
+      <c r="J30" s="2" t="n">
         <v>291729</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="2" t="n">
         <v>26444</v>
       </c>
     </row>
@@ -1491,34 +1479,34 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="3" t="n">
         <v>1.71</v>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="H31" s="4" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="I31" s="6" t="n">
-        <v>0.2452061889413495</v>
-      </c>
-      <c r="J31" s="3" t="n">
+      <c r="I31" s="5" t="n">
+        <v>0.2452061889413494</v>
+      </c>
+      <c r="J31" s="2" t="n">
         <v>262978</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="2" t="n">
         <v>4988</v>
       </c>
     </row>
@@ -1528,34 +1516,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" s="4" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="I32" s="6" t="n">
-        <v>0.9264859141728312</v>
-      </c>
-      <c r="J32" s="3" t="n">
+      <c r="I32" s="5" t="n">
+        <v>0.926485914172831</v>
+      </c>
+      <c r="J32" s="2" t="n">
         <v>68944</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="2" t="n">
         <v>7699</v>
       </c>
     </row>
@@ -1565,28 +1553,28 @@
           <t>fish_oil</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="5" t="n">
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="4" t="n">
         <v>47.9</v>
       </c>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="3" t="n">
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="2" t="n">
         <v>37289</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="2" t="n">
         <v>1735</v>
       </c>
     </row>
@@ -1596,34 +1584,34 @@
           <t>legumes</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H34" s="4" t="n">
         <v>62.4</v>
       </c>
-      <c r="I34" s="6" t="n">
-        <v>0.006170430008920973</v>
-      </c>
-      <c r="J34" s="3" t="n">
+      <c r="I34" s="5" t="n">
+        <v>0.00617043000892098</v>
+      </c>
+      <c r="J34" s="2" t="n">
         <v>1155076</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="2" t="n">
         <v>79072</v>
       </c>
     </row>
@@ -1633,34 +1621,34 @@
           <t>soluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="3" t="n">
         <v>1.39</v>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="6" t="n">
-        <v>0.188399637329524</v>
-      </c>
-      <c r="J35" s="3" t="n">
+      <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0.1883996373295245</v>
+      </c>
+      <c r="J35" s="2" t="n">
         <v>80888</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="2" t="n">
         <v>10851</v>
       </c>
     </row>
@@ -1670,34 +1658,34 @@
           <t>vitamin_b6</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
+      <c r="B36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="H36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>0.2443574036478493</v>
-      </c>
-      <c r="J36" s="3" t="n">
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0.2443574036478494</v>
+      </c>
+      <c r="J36" s="2" t="n">
         <v>70879</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="2" t="n">
         <v>7656</v>
       </c>
     </row>
@@ -1707,28 +1695,28 @@
           <t>plant_based_diet</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="5" t="n">
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="4" t="n">
         <v>39.5</v>
       </c>
-      <c r="I37" s="6" t="inlineStr"/>
-      <c r="J37" s="3" t="n">
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="2" t="n">
         <v>211318</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="2" t="n">
         <v>24516</v>
       </c>
     </row>
@@ -1738,28 +1726,28 @@
           <t>caffeine</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="4" t="n">
+      <c r="B38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr"/>
-      <c r="J38" s="3" t="n">
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="2" t="n">
         <v>46667</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K38" s="2" t="n">
         <v>3037</v>
       </c>
     </row>
@@ -1769,28 +1757,28 @@
           <t>ginseng</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="4" t="n">
+      <c r="B39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr"/>
-      <c r="J39" s="3" t="n">
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1800,34 +1788,34 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B40" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C40" s="4" t="n">
+      <c r="C40" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="E40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="4" t="n">
+      <c r="E40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="H40" s="5" t="n">
+      <c r="H40" s="4" t="n">
         <v>42.9</v>
       </c>
-      <c r="I40" s="6" t="n">
-        <v>0.07744276379719461</v>
-      </c>
-      <c r="J40" s="3" t="n">
+      <c r="I40" s="5" t="n">
+        <v>0.0774427637971946</v>
+      </c>
+      <c r="J40" s="2" t="n">
         <v>972077</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="2" t="n">
         <v>64899</v>
       </c>
     </row>
@@ -1837,34 +1825,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="3" t="n">
         <v>0.49</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="3" t="n">
         <v>1.77</v>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H41" s="4" t="n">
         <v>77.2</v>
       </c>
-      <c r="I41" s="6" t="n">
+      <c r="I41" s="5" t="n">
         <v>0.4656904115016954</v>
       </c>
-      <c r="J41" s="3" t="n">
+      <c r="J41" s="2" t="n">
         <v>121104</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="2" t="n">
         <v>7521</v>
       </c>
     </row>
@@ -1874,28 +1862,28 @@
           <t>ginkgo_biloba</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="5" t="n">
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="4" t="n">
         <v>46.8</v>
       </c>
-      <c r="I42" s="6" t="inlineStr"/>
-      <c r="J42" s="3" t="n">
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="2" t="n">
         <v>38308</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="2" t="n">
         <v>1665</v>
       </c>
     </row>
@@ -1905,34 +1893,34 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
+      <c r="B43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="H43" s="5" t="n">
+      <c r="H43" s="4" t="n">
         <v>55.4</v>
       </c>
-      <c r="I43" s="6" t="n">
+      <c r="I43" s="5" t="n">
         <v>0.6285558694668995</v>
       </c>
-      <c r="J43" s="3" t="n">
+      <c r="J43" s="2" t="n">
         <v>144141</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="2" t="n">
         <v>7729</v>
       </c>
     </row>
@@ -1942,34 +1930,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B44" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="C44" s="4" t="n">
+      <c r="C44" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="H44" s="5" t="n">
+      <c r="H44" s="4" t="n">
         <v>75.90000000000001</v>
       </c>
-      <c r="I44" s="6" t="n">
-        <v>0.1015950190265765</v>
-      </c>
-      <c r="J44" s="3" t="n">
+      <c r="I44" s="5" t="n">
+        <v>0.1015950190265767</v>
+      </c>
+      <c r="J44" s="2" t="n">
         <v>404649</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="2" t="n">
         <v>36660</v>
       </c>
     </row>
@@ -1979,28 +1967,28 @@
           <t>mediterranean_diet</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="4" t="n">
+      <c r="B45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr"/>
-      <c r="J45" s="3" t="n">
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="2" t="n">
         <v>47867</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="2" t="n">
         <v>6220</v>
       </c>
     </row>
@@ -2010,28 +1998,28 @@
           <t>dash_diet</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="4" t="n">
+      <c r="B46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="3" t="n">
         <v>1.04</v>
       </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="3" t="n">
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="2" t="n">
         <v>72784</v>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="K46" s="2" t="n">
         <v>1408</v>
       </c>
     </row>
@@ -2041,34 +2029,34 @@
           <t>omega_9_fatty_acids</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="4" t="n">
+      <c r="C47" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="3" t="n">
         <v>1.47</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="F47" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="3" t="n">
         <v>83.58</v>
       </c>
-      <c r="H47" s="5" t="n">
+      <c r="H47" s="4" t="n">
         <v>64.7</v>
       </c>
-      <c r="I47" s="6" t="n">
-        <v>0.8731289622544238</v>
-      </c>
-      <c r="J47" s="3" t="n">
+      <c r="I47" s="5" t="n">
+        <v>0.8731289622544243</v>
+      </c>
+      <c r="J47" s="2" t="n">
         <v>200953</v>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="K47" s="2" t="n">
         <v>7887</v>
       </c>
     </row>
@@ -2078,28 +2066,28 @@
           <t>plant_protein_intake</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="4" t="n">
+      <c r="B48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
-      <c r="H48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr"/>
-      <c r="J48" s="3" t="n">
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="2" t="n">
         <v>150671</v>
       </c>
-      <c r="K48" s="3" t="n">
+      <c r="K48" s="2" t="n">
         <v>14238</v>
       </c>
     </row>
@@ -2109,28 +2097,28 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="4" t="n">
+      <c r="B49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
-      <c r="H49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr"/>
-      <c r="J49" s="3" t="n">
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="2" t="n">
         <v>159482</v>
       </c>
-      <c r="K49" s="3" t="n">
+      <c r="K49" s="2" t="n">
         <v>17349</v>
       </c>
     </row>
@@ -2140,28 +2128,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n">
+      <c r="B50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="4" t="n">
+      <c r="C50" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
-      <c r="H50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="6" t="inlineStr"/>
-      <c r="J50" s="3" t="n">
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="2" t="n">
         <v>109557</v>
       </c>
-      <c r="K50" s="3" t="n">
+      <c r="K50" s="2" t="n">
         <v>3064</v>
       </c>
     </row>
@@ -2171,34 +2159,34 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="C51" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="F51" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="H51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="6" t="n">
+      <c r="H51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="5" t="n">
         <v>0.8121269612161565</v>
       </c>
-      <c r="J51" s="3" t="n">
+      <c r="J51" s="2" t="n">
         <v>900752</v>
       </c>
-      <c r="K51" s="3" t="n">
+      <c r="K51" s="2" t="n">
         <v>53381</v>
       </c>
     </row>
@@ -2208,34 +2196,34 @@
           <t>eicosapentaenoic_acid</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n">
+      <c r="B52" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C52" s="4" t="n">
+      <c r="C52" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="E52" s="4" t="n">
+      <c r="E52" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="F52" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="H52" s="5" t="n">
+      <c r="H52" s="4" t="n">
         <v>65.2</v>
       </c>
-      <c r="I52" s="6" t="n">
-        <v>0.5746798036256722</v>
-      </c>
-      <c r="J52" s="3" t="n">
+      <c r="I52" s="5" t="n">
+        <v>0.5746798036256719</v>
+      </c>
+      <c r="J52" s="2" t="n">
         <v>444156</v>
       </c>
-      <c r="K52" s="3" t="n">
+      <c r="K52" s="2" t="n">
         <v>13552</v>
       </c>
     </row>
@@ -2245,28 +2233,28 @@
           <t>docosapentaenoic_acid_omega_3</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n">
+      <c r="B53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="4" t="n">
+      <c r="C53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="E53" s="4" t="n">
+      <c r="E53" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr"/>
-      <c r="H53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr"/>
-      <c r="J53" s="3" t="n">
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="2" t="n">
         <v>143344</v>
       </c>
-      <c r="K53" s="3" t="n">
+      <c r="K53" s="2" t="n">
         <v>7412</v>
       </c>
     </row>
@@ -2276,34 +2264,34 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n">
+      <c r="B54" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="4" t="n">
+      <c r="C54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="n">
         <v>0.63</v>
       </c>
-      <c r="E54" s="4" t="n">
+      <c r="E54" s="3" t="n">
         <v>1.61</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="F54" s="3" t="n">
         <v>0.18</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="3" t="n">
         <v>5.71</v>
       </c>
-      <c r="H54" s="5" t="n">
+      <c r="H54" s="4" t="n">
         <v>84.2</v>
       </c>
-      <c r="I54" s="6" t="n">
-        <v>0.9535391069907841</v>
-      </c>
-      <c r="J54" s="3" t="n">
+      <c r="I54" s="5" t="n">
+        <v>0.9535391069907844</v>
+      </c>
+      <c r="J54" s="2" t="n">
         <v>3128</v>
       </c>
-      <c r="K54" s="3" t="n">
+      <c r="K54" s="2" t="n">
         <v>1292</v>
       </c>
     </row>
@@ -2313,28 +2301,28 @@
           <t>gondoic_acid</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="4" t="n">
+      <c r="B55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E55" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="4" t="inlineStr"/>
-      <c r="H55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="6" t="inlineStr"/>
-      <c r="J55" s="3" t="n">
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="2" t="n">
         <v>142239</v>
       </c>
-      <c r="K55" s="3" t="n">
+      <c r="K55" s="2" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2344,34 +2332,34 @@
           <t>multivitamin</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n">
+      <c r="B56" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="C56" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E56" s="3" t="n">
         <v>1.04</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="H56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="6" t="n">
+      <c r="H56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5" t="n">
         <v>0.9082727513733182</v>
       </c>
-      <c r="J56" s="3" t="n">
+      <c r="J56" s="2" t="n">
         <v>54340</v>
       </c>
-      <c r="K56" s="3" t="n">
+      <c r="K56" s="2" t="n">
         <v>5633</v>
       </c>
     </row>
@@ -2381,34 +2369,34 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n">
+      <c r="B57" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="C57" s="4" t="n">
+      <c r="C57" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E57" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="F57" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="3" t="n">
         <v>1.18</v>
       </c>
-      <c r="H57" s="5" t="n">
+      <c r="H57" s="4" t="n">
         <v>74.3</v>
       </c>
-      <c r="I57" s="6" t="n">
-        <v>0.9513120562303943</v>
-      </c>
-      <c r="J57" s="3" t="n">
+      <c r="I57" s="5" t="n">
+        <v>0.9513120562303942</v>
+      </c>
+      <c r="J57" s="2" t="n">
         <v>560815</v>
       </c>
-      <c r="K57" s="3" t="n">
+      <c r="K57" s="2" t="n">
         <v>31749</v>
       </c>
     </row>
@@ -2418,28 +2406,28 @@
           <t>betaine</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" s="4" t="n">
+      <c r="B58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="E58" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
-      <c r="H58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr"/>
-      <c r="J58" s="3" t="n">
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="2" t="n">
         <v>47896</v>
       </c>
-      <c r="K58" s="3" t="n">
+      <c r="K58" s="2" t="n">
         <v>695</v>
       </c>
     </row>
@@ -2449,34 +2437,34 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n">
+      <c r="B59" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="C59" s="4" t="n">
+      <c r="C59" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F59" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="H59" s="5" t="n">
+      <c r="H59" s="4" t="n">
         <v>80.8</v>
       </c>
-      <c r="I59" s="6" t="n">
-        <v>0.9371596744819083</v>
-      </c>
-      <c r="J59" s="3" t="n">
+      <c r="I59" s="5" t="n">
+        <v>0.9371596744819082</v>
+      </c>
+      <c r="J59" s="2" t="n">
         <v>568081</v>
       </c>
-      <c r="K59" s="3" t="n">
+      <c r="K59" s="2" t="n">
         <v>36597</v>
       </c>
     </row>
@@ -2486,34 +2474,34 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B60" s="3" t="n">
+      <c r="B60" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C60" s="4" t="n">
+      <c r="C60" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="E60" s="4" t="n">
+      <c r="E60" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="F60" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="H60" s="5" t="n">
+      <c r="H60" s="4" t="n">
         <v>38.1</v>
       </c>
-      <c r="I60" s="6" t="n">
-        <v>0.4142673366090839</v>
-      </c>
-      <c r="J60" s="3" t="n">
+      <c r="I60" s="5" t="n">
+        <v>0.4142673366090832</v>
+      </c>
+      <c r="J60" s="2" t="n">
         <v>248736</v>
       </c>
-      <c r="K60" s="3" t="n">
+      <c r="K60" s="2" t="n">
         <v>13760</v>
       </c>
     </row>
@@ -2523,28 +2511,28 @@
           <t>vitamin_k1</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="4" t="n">
+      <c r="B61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr"/>
-      <c r="H61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr"/>
-      <c r="J61" s="3" t="n">
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="2" t="n">
         <v>11319</v>
       </c>
-      <c r="K61" s="3" t="n">
+      <c r="K61" s="2" t="n">
         <v>268</v>
       </c>
     </row>
@@ -2554,34 +2542,34 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n">
+      <c r="B62" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C62" s="4" t="n">
+      <c r="C62" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="E62" s="4" t="n">
+      <c r="E62" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="F62" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="3" t="n">
         <v>1.26</v>
       </c>
-      <c r="H62" s="5" t="n">
+      <c r="H62" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="I62" s="6" t="n">
+      <c r="I62" s="5" t="n">
         <v>0.1931737969450245</v>
       </c>
-      <c r="J62" s="3" t="n">
+      <c r="J62" s="2" t="n">
         <v>91771</v>
       </c>
-      <c r="K62" s="3" t="n">
+      <c r="K62" s="2" t="n">
         <v>19124</v>
       </c>
     </row>
@@ -2591,28 +2579,28 @@
           <t>saw_palmetto</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" s="4" t="n">
+      <c r="B63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E63" s="4" t="n">
+      <c r="E63" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr"/>
-      <c r="H63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="6" t="inlineStr"/>
-      <c r="J63" s="3" t="n">
+      <c r="F63" s="3" t="inlineStr"/>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K63" s="3" t="n">
+      <c r="K63" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2622,28 +2610,28 @@
           <t>chondroitin</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" s="4" t="n">
+      <c r="B64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E64" s="4" t="n">
+      <c r="E64" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="4" t="inlineStr"/>
-      <c r="H64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr"/>
-      <c r="J64" s="3" t="n">
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K64" s="3" t="n">
+      <c r="K64" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2653,28 +2641,28 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n">
+      <c r="B65" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C65" s="4" t="n">
+      <c r="C65" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="4" t="n">
+      <c r="D65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F65" s="4" t="inlineStr"/>
-      <c r="G65" s="4" t="inlineStr"/>
-      <c r="H65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr"/>
-      <c r="J65" s="3" t="n">
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="2" t="n">
         <v>43360</v>
       </c>
-      <c r="K65" s="3" t="n">
+      <c r="K65" s="2" t="n">
         <v>6174</v>
       </c>
     </row>
@@ -2684,34 +2672,34 @@
           <t>iron</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n">
+      <c r="B66" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C66" s="4" t="n">
+      <c r="C66" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E66" s="4" t="n">
+      <c r="E66" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="F66" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="H66" s="5" t="n">
+      <c r="H66" s="4" t="n">
         <v>77.7</v>
       </c>
-      <c r="I66" s="6" t="n">
+      <c r="I66" s="5" t="n">
         <v>0.8981574513904264</v>
       </c>
-      <c r="J66" s="3" t="n">
+      <c r="J66" s="2" t="n">
         <v>184031</v>
       </c>
-      <c r="K66" s="3" t="n">
+      <c r="K66" s="2" t="n">
         <v>11578</v>
       </c>
     </row>
@@ -2721,28 +2709,28 @@
           <t>mineral_supplements</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="4" t="n">
+      <c r="B67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="F67" s="4" t="inlineStr"/>
-      <c r="G67" s="4" t="inlineStr"/>
-      <c r="H67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="6" t="inlineStr"/>
-      <c r="J67" s="3" t="n">
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="2" t="n">
         <v>10011</v>
       </c>
-      <c r="K67" s="3" t="n">
+      <c r="K67" s="2" t="n">
         <v>815</v>
       </c>
     </row>
@@ -2752,34 +2740,34 @@
           <t>glucosamine</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n">
+      <c r="B68" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C68" s="4" t="n">
+      <c r="C68" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="E68" s="4" t="n">
+      <c r="E68" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F68" s="4" t="n">
+      <c r="F68" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="3" t="n">
         <v>1.43</v>
       </c>
-      <c r="H68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="6" t="n">
-        <v>0.01558217739312316</v>
-      </c>
-      <c r="J68" s="3" t="n">
+      <c r="H68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0.01558217739312319</v>
+      </c>
+      <c r="J68" s="2" t="n">
         <v>265129</v>
       </c>
-      <c r="K68" s="3" t="n">
+      <c r="K68" s="2" t="n">
         <v>16136</v>
       </c>
     </row>
@@ -2789,28 +2777,28 @@
           <t>magnesium</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n">
+      <c r="B69" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C69" s="4" t="n">
+      <c r="C69" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="D69" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr"/>
-      <c r="H69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr"/>
-      <c r="J69" s="3" t="n">
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="2" t="n">
         <v>43795</v>
       </c>
-      <c r="K69" s="3" t="n">
+      <c r="K69" s="2" t="n">
         <v>6400</v>
       </c>
     </row>
@@ -2820,34 +2808,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n">
+      <c r="B70" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C70" s="4" t="n">
+      <c r="C70" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="E70" s="4" t="n">
+      <c r="E70" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="F70" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="3" t="n">
         <v>1.29</v>
       </c>
-      <c r="H70" s="5" t="n">
+      <c r="H70" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="I70" s="6" t="n">
-        <v>0.02415446339162438</v>
-      </c>
-      <c r="J70" s="3" t="n">
+      <c r="I70" s="5" t="n">
+        <v>0.02415446339162439</v>
+      </c>
+      <c r="J70" s="2" t="n">
         <v>1089615</v>
       </c>
-      <c r="K70" s="3" t="n">
+      <c r="K70" s="2" t="n">
         <v>64702</v>
       </c>
     </row>
@@ -2857,28 +2845,28 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B71" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" s="4" t="n">
+      <c r="B71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr"/>
-      <c r="H71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr"/>
-      <c r="J71" s="3" t="n">
+      <c r="F71" s="3" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="5" t="inlineStr"/>
+      <c r="J71" s="2" t="n">
         <v>21533</v>
       </c>
-      <c r="K71" s="3" t="n">
+      <c r="K71" s="2" t="n">
         <v>291</v>
       </c>
     </row>
@@ -2888,28 +2876,28 @@
           <t>vitamin_b2</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="4" t="n">
+      <c r="B72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="D72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="4" t="n">
+      <c r="D72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F72" s="4" t="inlineStr"/>
-      <c r="G72" s="4" t="inlineStr"/>
-      <c r="H72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="6" t="inlineStr"/>
-      <c r="J72" s="3" t="n">
+      <c r="F72" s="3" t="inlineStr"/>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="5" t="inlineStr"/>
+      <c r="J72" s="2" t="n">
         <v>1595</v>
       </c>
-      <c r="K72" s="3" t="n">
+      <c r="K72" s="2" t="n">
         <v>561</v>
       </c>
     </row>
@@ -2919,34 +2907,34 @@
           <t>whole_grain_intake</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n">
+      <c r="B73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C73" s="4" t="n">
+      <c r="C73" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="D73" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="3" t="n">
         <v>1.26</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="F73" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="3" t="n">
         <v>5.08</v>
       </c>
-      <c r="H73" s="5" t="n">
+      <c r="H73" s="4" t="n">
         <v>83.3</v>
       </c>
-      <c r="I73" s="6" t="n">
+      <c r="I73" s="5" t="n">
         <v>0.1158775811071888</v>
       </c>
-      <c r="J73" s="3" t="n">
+      <c r="J73" s="2" t="n">
         <v>79458</v>
       </c>
-      <c r="K73" s="3" t="n">
+      <c r="K73" s="2" t="n">
         <v>7209</v>
       </c>
     </row>
@@ -2956,28 +2944,28 @@
           <t>phosphorus</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C74" s="4" t="n">
+      <c r="B74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F74" s="4" t="inlineStr"/>
-      <c r="G74" s="4" t="inlineStr"/>
-      <c r="H74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="6" t="inlineStr"/>
-      <c r="J74" s="3" t="n">
+      <c r="F74" s="3" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="5" t="inlineStr"/>
+      <c r="J74" s="2" t="n">
         <v>47885</v>
       </c>
-      <c r="K74" s="3" t="n">
+      <c r="K74" s="2" t="n">
         <v>5861</v>
       </c>
     </row>
@@ -2987,34 +2975,34 @@
           <t>vitamin_b12</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n">
+      <c r="B75" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C75" s="4" t="n">
+      <c r="C75" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" s="3" t="n">
         <v>0.73</v>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="3" t="n">
         <v>1.71</v>
       </c>
-      <c r="H75" s="5" t="n">
+      <c r="H75" s="4" t="n">
         <v>64.5</v>
       </c>
-      <c r="I75" s="6" t="n">
-        <v>0.0114501930016075</v>
-      </c>
-      <c r="J75" s="3" t="n">
+      <c r="I75" s="5" t="n">
+        <v>0.01145019300160749</v>
+      </c>
+      <c r="J75" s="2" t="n">
         <v>5961</v>
       </c>
-      <c r="K75" s="3" t="n">
+      <c r="K75" s="2" t="n">
         <v>2681</v>
       </c>
     </row>
@@ -3024,34 +3012,34 @@
           <t>zinc</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n">
+      <c r="B76" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="C76" s="4" t="n">
+      <c r="C76" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="E76" s="4" t="n">
+      <c r="E76" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="3" t="n">
         <v>3.01</v>
       </c>
-      <c r="H76" s="5" t="n">
+      <c r="H76" s="4" t="n">
         <v>80.5</v>
       </c>
-      <c r="I76" s="6" t="n">
-        <v>0.5211814544747839</v>
-      </c>
-      <c r="J76" s="3" t="n">
+      <c r="I76" s="5" t="n">
+        <v>0.5211814544747837</v>
+      </c>
+      <c r="J76" s="2" t="n">
         <v>49478</v>
       </c>
-      <c r="K76" s="3" t="n">
+      <c r="K76" s="2" t="n">
         <v>6840</v>
       </c>
     </row>
@@ -3061,34 +3049,34 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n">
+      <c r="B77" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="C77" s="4" t="n">
+      <c r="C77" s="3" t="n">
         <v>1.14</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="F77" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="3" t="n">
         <v>1.53</v>
       </c>
-      <c r="H77" s="5" t="n">
+      <c r="H77" s="4" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="I77" s="6" t="n">
-        <v>0.04932265398703133</v>
-      </c>
-      <c r="J77" s="3" t="n">
+      <c r="I77" s="5" t="n">
+        <v>0.04932265398703134</v>
+      </c>
+      <c r="J77" s="2" t="n">
         <v>951593</v>
       </c>
-      <c r="K77" s="3" t="n">
+      <c r="K77" s="2" t="n">
         <v>55176</v>
       </c>
     </row>
@@ -3098,34 +3086,34 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B78" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="C78" s="4" t="n">
+      <c r="C78" s="3" t="n">
         <v>1.14</v>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="D78" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="E78" s="4" t="n">
+      <c r="E78" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="F78" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="3" t="n">
         <v>1.38</v>
       </c>
-      <c r="H78" s="5" t="n">
+      <c r="H78" s="4" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="I78" s="6" t="n">
-        <v>0.01640873960670477</v>
-      </c>
-      <c r="J78" s="3" t="n">
+      <c r="I78" s="5" t="n">
+        <v>0.01640873960670482</v>
+      </c>
+      <c r="J78" s="2" t="n">
         <v>547664</v>
       </c>
-      <c r="K78" s="3" t="n">
+      <c r="K78" s="2" t="n">
         <v>63207</v>
       </c>
     </row>
@@ -3135,34 +3123,34 @@
           <t>alpha_linolenic_acid</t>
         </is>
       </c>
-      <c r="B79" s="3" t="n">
+      <c r="B79" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C79" s="4" t="n">
+      <c r="C79" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="D79" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="E79" s="4" t="n">
+      <c r="E79" s="3" t="n">
         <v>1.43</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F79" s="3" t="n">
         <v>0.58</v>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="3" t="n">
         <v>2.27</v>
       </c>
-      <c r="H79" s="5" t="n">
+      <c r="H79" s="4" t="n">
         <v>77.2</v>
       </c>
-      <c r="I79" s="6" t="n">
-        <v>0.2932566086946219</v>
-      </c>
-      <c r="J79" s="3" t="n">
+      <c r="I79" s="5" t="n">
+        <v>0.2932566086946222</v>
+      </c>
+      <c r="J79" s="2" t="n">
         <v>173827</v>
       </c>
-      <c r="K79" s="3" t="n">
+      <c r="K79" s="2" t="n">
         <v>9647</v>
       </c>
     </row>
@@ -3172,34 +3160,34 @@
           <t>antioxidants</t>
         </is>
       </c>
-      <c r="B80" s="3" t="n">
+      <c r="B80" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C80" s="4" t="n">
+      <c r="C80" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="D80" s="4" t="n">
+      <c r="D80" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="E80" s="4" t="n">
+      <c r="E80" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="F80" s="3" t="n">
         <v>0.04</v>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="3" t="n">
         <v>33.17</v>
       </c>
-      <c r="H80" s="5" t="n">
+      <c r="H80" s="4" t="n">
         <v>90.3</v>
       </c>
-      <c r="I80" s="6" t="n">
+      <c r="I80" s="5" t="n">
         <v>0.1648989938761477</v>
       </c>
-      <c r="J80" s="3" t="n">
+      <c r="J80" s="2" t="n">
         <v>56601</v>
       </c>
-      <c r="K80" s="3" t="n">
+      <c r="K80" s="2" t="n">
         <v>7271</v>
       </c>
     </row>
@@ -3209,34 +3197,34 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B81" s="3" t="n">
+      <c r="B81" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="C81" s="4" t="n">
+      <c r="C81" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="D81" s="4" t="n">
+      <c r="D81" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E81" s="4" t="n">
+      <c r="E81" s="3" t="n">
         <v>1.42</v>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="F81" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="3" t="n">
         <v>2.43</v>
       </c>
-      <c r="H81" s="5" t="n">
+      <c r="H81" s="4" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="I81" s="6" t="n">
-        <v>0.9490649069662661</v>
-      </c>
-      <c r="J81" s="3" t="n">
+      <c r="I81" s="5" t="n">
+        <v>0.9490649069662658</v>
+      </c>
+      <c r="J81" s="2" t="n">
         <v>70012</v>
       </c>
-      <c r="K81" s="3" t="n">
+      <c r="K81" s="2" t="n">
         <v>17837</v>
       </c>
     </row>
@@ -3246,28 +3234,28 @@
           <t>choline</t>
         </is>
       </c>
-      <c r="B82" s="3" t="n">
+      <c r="B82" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C82" s="4" t="n">
+      <c r="C82" s="3" t="n">
         <v>1.18</v>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="D82" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="E82" s="4" t="n">
+      <c r="E82" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr"/>
-      <c r="H82" s="5" t="n">
+      <c r="F82" s="3" t="inlineStr"/>
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="4" t="n">
         <v>71.2</v>
       </c>
-      <c r="I82" s="6" t="inlineStr"/>
-      <c r="J82" s="3" t="n">
+      <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="2" t="n">
         <v>8123</v>
       </c>
-      <c r="K82" s="3" t="n">
+      <c r="K82" s="2" t="n">
         <v>1372</v>
       </c>
     </row>
@@ -3277,34 +3265,34 @@
           <t>coenzyme_q10</t>
         </is>
       </c>
-      <c r="B83" s="3" t="n">
+      <c r="B83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C83" s="4" t="n">
+      <c r="C83" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="D83" s="4" t="n">
+      <c r="D83" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E83" s="4" t="n">
+      <c r="E83" s="3" t="n">
         <v>1.79</v>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="F83" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="3" t="n">
         <v>119.97</v>
       </c>
-      <c r="H83" s="5" t="n">
+      <c r="H83" s="4" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="I83" s="6" t="n">
-        <v>0.3692661628018608</v>
-      </c>
-      <c r="J83" s="3" t="n">
+      <c r="I83" s="5" t="n">
+        <v>0.3692661628018609</v>
+      </c>
+      <c r="J83" s="2" t="n">
         <v>36416</v>
       </c>
-      <c r="K83" s="3" t="n">
+      <c r="K83" s="2" t="n">
         <v>2065</v>
       </c>
     </row>
@@ -3314,34 +3302,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B84" s="3" t="n">
+      <c r="B84" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="C84" s="4" t="n">
+      <c r="C84" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="D84" s="4" t="n">
+      <c r="D84" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="E84" s="4" t="n">
+      <c r="E84" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="F84" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="3" t="n">
         <v>1.66</v>
       </c>
-      <c r="H84" s="5" t="n">
+      <c r="H84" s="4" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="I84" s="6" t="n">
+      <c r="I84" s="5" t="n">
         <v>0.005223613003526282</v>
       </c>
-      <c r="J84" s="3" t="n">
+      <c r="J84" s="2" t="n">
         <v>1911711</v>
       </c>
-      <c r="K84" s="3" t="n">
+      <c r="K84" s="2" t="n">
         <v>47035</v>
       </c>
     </row>
@@ -3351,34 +3339,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B85" s="3" t="n">
+      <c r="B85" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="C85" s="4" t="n">
+      <c r="C85" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="D85" s="4" t="n">
+      <c r="D85" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="E85" s="4" t="n">
+      <c r="E85" s="3" t="n">
         <v>1.34</v>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="F85" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="3" t="n">
         <v>1.79</v>
       </c>
-      <c r="H85" s="5" t="n">
+      <c r="H85" s="4" t="n">
         <v>83.3</v>
       </c>
-      <c r="I85" s="6" t="n">
-        <v>0.118225546377741</v>
-      </c>
-      <c r="J85" s="3" t="n">
+      <c r="I85" s="5" t="n">
+        <v>0.1182255463777411</v>
+      </c>
+      <c r="J85" s="2" t="n">
         <v>688143</v>
       </c>
-      <c r="K85" s="3" t="n">
+      <c r="K85" s="2" t="n">
         <v>33749</v>
       </c>
     </row>
@@ -3388,28 +3376,28 @@
           <t>glutamine</t>
         </is>
       </c>
-      <c r="B86" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="4" t="n">
+      <c r="B86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="D86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="4" t="n">
+      <c r="D86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="F86" s="4" t="inlineStr"/>
-      <c r="G86" s="4" t="inlineStr"/>
-      <c r="H86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr"/>
-      <c r="J86" s="3" t="n">
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr"/>
+      <c r="H86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="5" t="inlineStr"/>
+      <c r="J86" s="2" t="n">
         <v>342</v>
       </c>
-      <c r="K86" s="3" t="n">
+      <c r="K86" s="2" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3419,34 +3407,34 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B87" s="3" t="n">
+      <c r="B87" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C87" s="4" t="n">
+      <c r="C87" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="D87" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="4" t="n">
+      <c r="D87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F87" s="3" t="n">
         <v>0.12</v>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="3" t="n">
         <v>12.86</v>
       </c>
-      <c r="H87" s="5" t="n">
+      <c r="H87" s="4" t="n">
         <v>50.3</v>
       </c>
-      <c r="I87" s="6" t="n">
-        <v>0.257220017732754</v>
-      </c>
-      <c r="J87" s="3" t="n">
+      <c r="I87" s="5" t="n">
+        <v>0.2572200177327541</v>
+      </c>
+      <c r="J87" s="2" t="n">
         <v>201324</v>
       </c>
-      <c r="K87" s="3" t="n">
+      <c r="K87" s="2" t="n">
         <v>7680</v>
       </c>
     </row>
@@ -3456,34 +3444,34 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B88" s="3" t="n">
+      <c r="B88" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C88" s="4" t="n">
+      <c r="C88" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="D88" s="4" t="n">
+      <c r="D88" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="E88" s="4" t="n">
+      <c r="E88" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="F88" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="3" t="n">
         <v>2.04</v>
       </c>
-      <c r="H88" s="5" t="n">
+      <c r="H88" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="I88" s="6" t="n">
-        <v>0.084534645965818</v>
-      </c>
-      <c r="J88" s="3" t="n">
+      <c r="I88" s="5" t="n">
+        <v>0.08453464596581801</v>
+      </c>
+      <c r="J88" s="2" t="n">
         <v>255534</v>
       </c>
-      <c r="K88" s="3" t="n">
+      <c r="K88" s="2" t="n">
         <v>13888</v>
       </c>
     </row>
@@ -3493,28 +3481,28 @@
           <t>creatine</t>
         </is>
       </c>
-      <c r="B89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C89" s="4" t="n">
+      <c r="B89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="D89" s="4" t="n">
+      <c r="D89" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="E89" s="4" t="n">
+      <c r="E89" s="3" t="n">
         <v>1.63</v>
       </c>
-      <c r="F89" s="4" t="inlineStr"/>
-      <c r="G89" s="4" t="inlineStr"/>
-      <c r="H89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr"/>
-      <c r="J89" s="3" t="n">
+      <c r="F89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="5" t="inlineStr"/>
+      <c r="J89" s="2" t="n">
         <v>342</v>
       </c>
-      <c r="K89" s="3" t="n">
+      <c r="K89" s="2" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3524,28 +3512,28 @@
           <t>l_valine</t>
         </is>
       </c>
-      <c r="B90" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" s="4" t="n">
+      <c r="B90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="D90" s="4" t="n">
+      <c r="D90" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="E90" s="4" t="n">
+      <c r="E90" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="F90" s="4" t="inlineStr"/>
-      <c r="G90" s="4" t="inlineStr"/>
-      <c r="H90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="6" t="inlineStr"/>
-      <c r="J90" s="3" t="n">
+      <c r="F90" s="3" t="inlineStr"/>
+      <c r="G90" s="3" t="inlineStr"/>
+      <c r="H90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="5" t="inlineStr"/>
+      <c r="J90" s="2" t="n">
         <v>342</v>
       </c>
-      <c r="K90" s="3" t="n">
+      <c r="K90" s="2" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3555,28 +3543,28 @@
           <t>l_tyrosine</t>
         </is>
       </c>
-      <c r="B91" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" s="4" t="n">
+      <c r="B91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="D91" s="4" t="n">
+      <c r="D91" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="E91" s="4" t="n">
+      <c r="E91" s="3" t="n">
         <v>1.66</v>
       </c>
-      <c r="F91" s="4" t="inlineStr"/>
-      <c r="G91" s="4" t="inlineStr"/>
-      <c r="H91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="6" t="inlineStr"/>
-      <c r="J91" s="3" t="n">
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr"/>
+      <c r="H91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="5" t="inlineStr"/>
+      <c r="J91" s="2" t="n">
         <v>342</v>
       </c>
-      <c r="K91" s="3" t="n">
+      <c r="K91" s="2" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3586,28 +3574,28 @@
           <t>chocolate</t>
         </is>
       </c>
-      <c r="B92" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" s="4" t="n">
+      <c r="B92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="D92" s="4" t="n">
+      <c r="D92" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="E92" s="4" t="n">
+      <c r="E92" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="F92" s="4" t="inlineStr"/>
-      <c r="G92" s="4" t="inlineStr"/>
-      <c r="H92" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="6" t="inlineStr"/>
-      <c r="J92" s="3" t="n">
+      <c r="F92" s="3" t="inlineStr"/>
+      <c r="G92" s="3" t="inlineStr"/>
+      <c r="H92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="5" t="inlineStr"/>
+      <c r="J92" s="2" t="n">
         <v>2611</v>
       </c>
-      <c r="K92" s="3" t="n">
+      <c r="K92" s="2" t="n">
         <v>1499</v>
       </c>
     </row>
@@ -3617,28 +3605,28 @@
           <t>western_pattern_diet</t>
         </is>
       </c>
-      <c r="B93" s="3" t="n">
+      <c r="B93" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C93" s="4" t="n">
+      <c r="C93" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="D93" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="4" t="n">
+      <c r="D93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="F93" s="4" t="inlineStr"/>
-      <c r="G93" s="4" t="inlineStr"/>
-      <c r="H93" s="5" t="n">
+      <c r="F93" s="3" t="inlineStr"/>
+      <c r="G93" s="3" t="inlineStr"/>
+      <c r="H93" s="4" t="n">
         <v>57.1</v>
       </c>
-      <c r="I93" s="6" t="inlineStr"/>
-      <c r="J93" s="3" t="n">
+      <c r="I93" s="5" t="inlineStr"/>
+      <c r="J93" s="2" t="n">
         <v>44462</v>
       </c>
-      <c r="K93" s="3" t="n">
+      <c r="K93" s="2" t="n">
         <v>1702</v>
       </c>
     </row>
@@ -3648,34 +3636,34 @@
           <t>fermented_foods</t>
         </is>
       </c>
-      <c r="B94" s="3" t="n">
+      <c r="B94" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C94" s="4" t="n">
+      <c r="C94" s="3" t="n">
         <v>1.37</v>
       </c>
-      <c r="D94" s="4" t="n">
+      <c r="D94" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="E94" s="4" t="n">
+      <c r="E94" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="F94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="4" t="n">
+      <c r="F94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="n">
         <v>664.3099999999999</v>
       </c>
-      <c r="H94" s="5" t="n">
+      <c r="H94" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="I94" s="6" t="n">
-        <v>0.1814798483236068</v>
-      </c>
-      <c r="J94" s="3" t="n">
+      <c r="I94" s="5" t="n">
+        <v>0.1814798483236069</v>
+      </c>
+      <c r="J94" s="2" t="n">
         <v>3460</v>
       </c>
-      <c r="K94" s="3" t="n">
+      <c r="K94" s="2" t="n">
         <v>339</v>
       </c>
     </row>
@@ -3685,28 +3673,28 @@
           <t>gamma_linolenic_acid</t>
         </is>
       </c>
-      <c r="B95" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" s="4" t="n">
+      <c r="B95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="D95" s="4" t="n">
+      <c r="D95" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E95" s="4" t="n">
+      <c r="E95" s="3" t="n">
         <v>2.12</v>
       </c>
-      <c r="F95" s="4" t="inlineStr"/>
-      <c r="G95" s="4" t="inlineStr"/>
-      <c r="H95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="6" t="inlineStr"/>
-      <c r="J95" s="3" t="n">
+      <c r="F95" s="3" t="inlineStr"/>
+      <c r="G95" s="3" t="inlineStr"/>
+      <c r="H95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="5" t="inlineStr"/>
+      <c r="J95" s="2" t="n">
         <v>952</v>
       </c>
-      <c r="K95" s="3" t="n">
+      <c r="K95" s="2" t="n">
         <v>476</v>
       </c>
     </row>
@@ -3716,28 +3704,28 @@
           <t>dihomo_gamma_linolenic_acid</t>
         </is>
       </c>
-      <c r="B96" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" s="4" t="n">
+      <c r="B96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="3" t="n">
         <v>1.54</v>
       </c>
-      <c r="D96" s="4" t="n">
+      <c r="D96" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="E96" s="4" t="n">
+      <c r="E96" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="F96" s="4" t="inlineStr"/>
-      <c r="G96" s="4" t="inlineStr"/>
-      <c r="H96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="6" t="inlineStr"/>
-      <c r="J96" s="3" t="n">
+      <c r="F96" s="3" t="inlineStr"/>
+      <c r="G96" s="3" t="inlineStr"/>
+      <c r="H96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="5" t="inlineStr"/>
+      <c r="J96" s="2" t="n">
         <v>952</v>
       </c>
-      <c r="K96" s="3" t="n">
+      <c r="K96" s="2" t="n">
         <v>476</v>
       </c>
     </row>
@@ -3747,34 +3735,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B97" s="3" t="n">
+      <c r="B97" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C97" s="4" t="n">
+      <c r="C97" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="D97" s="4" t="n">
+      <c r="D97" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="E97" s="4" t="n">
+      <c r="E97" s="3" t="n">
         <v>2.23</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F97" s="3" t="n">
         <v>0.49</v>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="3" t="n">
         <v>5.24</v>
       </c>
-      <c r="H97" s="5" t="n">
+      <c r="H97" s="4" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="I97" s="6" t="n">
-        <v>0.08121470978386684</v>
-      </c>
-      <c r="J97" s="3" t="n">
+      <c r="I97" s="5" t="n">
+        <v>0.08121470978386697</v>
+      </c>
+      <c r="J97" s="2" t="n">
         <v>873126</v>
       </c>
-      <c r="K97" s="3" t="n">
+      <c r="K97" s="2" t="n">
         <v>56254</v>
       </c>
     </row>
@@ -3784,28 +3772,28 @@
           <t>phosphatidylcholine</t>
         </is>
       </c>
-      <c r="B98" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" s="4" t="n">
+      <c r="B98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" s="3" t="n">
         <v>1.78</v>
       </c>
-      <c r="D98" s="4" t="n">
+      <c r="D98" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="E98" s="4" t="n">
+      <c r="E98" s="3" t="n">
         <v>2.87</v>
       </c>
-      <c r="F98" s="4" t="inlineStr"/>
-      <c r="G98" s="4" t="inlineStr"/>
-      <c r="H98" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="6" t="inlineStr"/>
-      <c r="J98" s="3" t="n">
+      <c r="F98" s="3" t="inlineStr"/>
+      <c r="G98" s="3" t="inlineStr"/>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="5" t="inlineStr"/>
+      <c r="J98" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="K98" s="3" t="n">
+      <c r="K98" s="2" t="n">
         <v>41</v>
       </c>
     </row>
@@ -3815,28 +3803,28 @@
           <t>glycine</t>
         </is>
       </c>
-      <c r="B99" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C99" s="4" t="n">
+      <c r="B99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="3" t="n">
         <v>1.84</v>
       </c>
-      <c r="D99" s="4" t="n">
+      <c r="D99" s="3" t="n">
         <v>1.18</v>
       </c>
-      <c r="E99" s="4" t="n">
+      <c r="E99" s="3" t="n">
         <v>2.72</v>
       </c>
-      <c r="F99" s="4" t="inlineStr"/>
-      <c r="G99" s="4" t="inlineStr"/>
-      <c r="H99" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr"/>
-      <c r="J99" s="3" t="n">
+      <c r="F99" s="3" t="inlineStr"/>
+      <c r="G99" s="3" t="inlineStr"/>
+      <c r="H99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="5" t="inlineStr"/>
+      <c r="J99" s="2" t="n">
         <v>666</v>
       </c>
-      <c r="K99" s="3" t="n">
+      <c r="K99" s="2" t="n">
         <v>333</v>
       </c>
     </row>
@@ -3846,28 +3834,28 @@
           <t>pickled_vegetables</t>
         </is>
       </c>
-      <c r="B100" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C100" s="4" t="n">
+      <c r="B100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="3" t="n">
         <v>4.58</v>
       </c>
-      <c r="D100" s="4" t="n">
+      <c r="D100" s="3" t="n">
         <v>2.97</v>
       </c>
-      <c r="E100" s="4" t="n">
+      <c r="E100" s="3" t="n">
         <v>5.94</v>
       </c>
-      <c r="F100" s="4" t="inlineStr"/>
-      <c r="G100" s="4" t="inlineStr"/>
-      <c r="H100" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="6" t="inlineStr"/>
-      <c r="J100" s="3" t="n">
+      <c r="F100" s="3" t="inlineStr"/>
+      <c r="G100" s="3" t="inlineStr"/>
+      <c r="H100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="5" t="inlineStr"/>
+      <c r="J100" s="2" t="n">
         <v>404</v>
       </c>
-      <c r="K100" s="3" t="n">
+      <c r="K100" s="2" t="n">
         <v>130</v>
       </c>
     </row>
